--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Agentic Production Coverage · R&amp;D Initiative Impact</t>
+          <t>Agentic Production Coverage</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Agentic Production Coverage · R&amp;D Initiative Impact · Cost per MCQ Generated · Cost per Coding Question</t>
+          <t>Agentic Production Coverage · Cost per MCQ Generated · Cost per Coding Question</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Pedagogy Initiative Impact · R&amp;D Initiative Impact</t>
+          <t>Pedagogy Initiative Impact · Agentic Production Coverage</t>
         </is>
       </c>
     </row>

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Wiring" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rating Framework" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Manager" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1834,12 +1835,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Operations &amp; Growth Cost · Creative Resource Utilisation Rate</t>
+          <t>Cost of Operations · Creative Resource Utilisation Rate</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Hygiene guardrails (PM-managed reads) — no org ladder by design.</t>
+          <t>Hygiene guardrails from the Team Ops &amp; People block — run by the team's PM; no org ladder by design.</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1910,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
+    <row r="23" ht="39" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
@@ -1920,14 +1921,14 @@
           <t>Mentorship</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>— (by design)</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Power Performers Created</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Rating Pillar 3 (Develop the Best) — deliberately review-based, no KPI row.</t>
+          <t>Rating Pillar 3 (Develop the Best) — first direct read: members made next-level-ready, counted per appraisal cycle. Feedback quality and growth opportunities stay review-based.</t>
         </is>
       </c>
     </row>
@@ -2245,9 +2246,9 @@
           <t>Members ready for next level, training program design</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Review-based — no KPI row by design</t>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Power Performers Created</t>
         </is>
       </c>
     </row>
@@ -2289,9 +2290,9 @@
           <t>Active participation, candidate evaluation quality, new hire success rate</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Review-based — no KPI row by design</t>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Hires Made · Cost per Hire</t>
         </is>
       </c>
     </row>
@@ -2311,9 +2312,9 @@
           <t>High potential recognition, development opportunities, succession planning</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Review-based — no KPI row by design</t>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Team Retention Rate</t>
         </is>
       </c>
     </row>
@@ -3367,4 +3368,274 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0E6E5C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project Manager — the team's operating seat (added August 2026 with the Team Ops &amp; People metric block). Not a ladder level: reports to the AI Engineer Lead.</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Title pattern</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Project Manager – [Domain] Learning Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Pilot instance</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Project Manager – FullStack &amp; CS Core Learning Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Reports to</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>The team's AI Engineer Lead. KPIs cascade Lead → PM: the Lead answers for the numbers at review; the PM runs them day to day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Comp</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Band pending — defined with HR when the seat is staffed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Owns (metric surface)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Cost of Operations · Roadmap Items Completion · Hires Made · Cost per Hire · Team Retention Rate · Power Performers Created · Creative Resource Utilisation Rate. The Team Ops &amp; People block of the team view — the FullStack &amp; CS Core pilot carries all 7 (CSI: 6, without the creative-utilisation row). Three of these are also the Lead's Develop-the-Best rating reads: the PM operates the rows, the Lead answers for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Interfaces</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Content–Central PMO: the PM feeds the monthly check-in — complete worklogs and current ClickUp statuses are what the PMO's Worklog &amp; Status Hygiene — All Units read counts. Worklog capture is the load-bearing activity: it makes deliverable costing computable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Progression / rating</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Progression and rating for the PM seat itself: not designed yet — this card fixes the seat, the reporting line and the metric surface first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Ops register — the activities inside Cost of Operations (so nothing is forgotten)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Monthly manager–reportee one-on-ones</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Scheduling roadmap review meetings + Head approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Day-to-day ops — standups, learning hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Scheduling monthly check-in meets &amp; documenting them in the right place</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Maintaining team assets (laptops, systems)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Ensuring ClickUp adoption</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Keeping deliverable statuses up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Monthly worklog capture → deliverable costs computed for the check-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Generating newsletters monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Conducting team outings</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Conducting cycle-wise appraisal meetings</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ladder" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Areas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Wiring" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rating Framework" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Manager" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates &amp; Scope" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Areas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Wiring" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rating Framework" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Manager" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +51,12 @@
     <font>
       <name val="Calibri"/>
       <color rgb="FF1A1A1A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
     <font>
@@ -102,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -121,6 +128,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -489,55 +499,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI Engineer Ladder — content-department domain teams · v2 August 2026 (titles renamed from the March 2026 SDE framework; descriptors verbatim)</t>
+          <t>AI Engineer Ladder — content-department domain teams · v3 August 2026 (internship rung · AI Engineer 1 + 2 merged · Senior AI Engineer added · descriptors from the March 2026 SDE framework; comp for changed rungs with HR)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Title (v2 pattern)</t>
+          <t>Title (v3 pattern)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Formerly</t>
+          <t>Formerly (source)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Comp | Experience</t>
+          <t>Comp | Tenure</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Role (v3)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Scope (source, examples retitled)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Metric surface (v2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Metric surface (v3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Associate AI Engineer – [Domain] Learning Systems</t>
@@ -550,24 +567,29 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>4.5L to 7L | 0-1 years</t>
+          <t>Internship stipend — set by HR | 6-month internship</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
+          <t>6-month internship — manages agents under supervision from day one: runs existing pipelines, reviews outputs, tunes prompts, handles escalations (A1), then shows measurable improvement on an agent's numbers (A2). Produces representative content items manually during the ramp — the domain floor. Converts through the gate below.</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
           <t>Example: "Associate AI Engineer – FullStack Learning Systems" or "Associate AI Engineer – GenAI Learning Systems". Creates content with guidance (lessons, exercises, projects, assessments). Learns to integrate code playgrounds, evaluation judges, and learning platforms. Handles 0.5-1 domain, 40-100 content hours, reaches 2K-5K students.</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Contributes to this team's Section B rows under review — no rows answered for yet; growth is read through review evidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="56" customHeight="1">
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Contributes on sample surfaces along the internship ramp — no rows answered for; growth is read through ramp evidence (A1→A2 on the Agent Scope scale).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer 1 – [Domain] Learning Systems</t>
+          <t>AI Engineer – [Domain] Learning Systems</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -577,24 +599,29 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>9L to 16L | 1-3+ years</t>
+          <t>9–24L, band under HR review (spans the two merged bands) | ≥1 year in role before Senior eligibility</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Example: "AI Engineer 1 – DS/ML Learning Systems". Creates domain content independently (lessons, exercises, projects). Engineers learning systems by selecting appropriate platforms (IDEs, cloud environments, assessment engines). Owns 1-2 domains. Manages 100-250 hours, reaches 5K-10K students.</t>
+          <t>Manages agents. Owns modules end-to-end and builds new content agents — 2–3 built and adopted by year-end, impact visible in the metrics (A3). One band: the old AI Engineer 1 and 2 merge here.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Answers for the Section B velocity + quality rows of the modules they own (their content hours, pieces, issue-recurrence share).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1">
+          <t>Example: "AI Engineer – DS/ML Learning Systems". Creates domain content independently (lessons, exercises, projects). Engineers learning systems by selecting appropriate platforms (IDEs, cloud environments, assessment engines). Owns 1-2 domains. Manages 100-250 hours, reaches 5K-10K students.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Answers for the Section B velocity + quality rows of the modules they own (their content hours, pieces, issue-recurrence share) — with 2–3 content agents built and adopted (A3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="84" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer 2 – [Domain Portfolio] Learning Systems</t>
+          <t>Senior AI Engineer – [Domain Portfolio] Learning Systems</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -604,21 +631,26 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>18L to 24L | 3+ years</t>
+          <t>Band under HR review — new rung | reached through the 2× gate below</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Example: "AI Engineer 2 – FullStack, System Design &amp; CS Core Learning Systems". Leads content creation across multiple domains. Architects platform systems and optimizes evaluation pipelines. Manages 2-5 team members across 3-4 domains. Manages 250-450 hours, reaches 10K-20K students.</t>
+          <t>Manages agent systems and mentors humans — the force-multiplier rung. Holds ≈2× an AI Engineer's complexity-weighted surface by depth, breadth, or leverage; orchestrating systems of agents (A4) is the leverage route. Invents new ways to teach with agentic AI and proves them with rigorous measurement.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Answers for a domain slice of Section B — effectiveness, velocity and Evaluation Environment Coverage for their courses; first Section C asks raised in their name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
+          <t>Example: "Senior AI Engineer – FullStack, System Design &amp; CS Core Learning Systems". Leads content creation across multiple domains. Architects platform systems and optimizes evaluation pipelines. Manages 2-5 team members across 3-4 domains. Manages 250-450 hours, reaches 10K-20K students.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Answers for a domain slice ≈ 2× an AI Engineer's complexity-weighted surface — by depth, breadth, or leverage (A4 agent systems); first Section C asks raised in their name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>AI Engineer Lead – [Domain Portfolio] Learning Systems</t>
@@ -636,16 +668,21 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
+          <t>Manages humans who manage agents. Runs the team: full Section B answered for at review; people outcomes — ratings, retention, growth, hiring — define the title. Span ~5–8 members (number with HR).</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
           <t>Example: "AI Engineer Lead – Programming, FullStack, CS Core, DevOps Learning Systems". Owns content strategy and creation across portfolio. Designs platform architecture and GenAI-driven content systems. Leads 15-25 members across 4-6 domains. Manages 450+ hours, reaches 20K-40K+ students.</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Answers for the team's full Section B at review and supports the Section A lane numbers; the rating framework below applies as written.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Answers for the team's full Section B at review and supports the Section A lane numbers; span ~5–8 members; the rating framework below applies as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>AI Engineer 3 – [Domain Portfolio] Learning Systems</t>
@@ -667,6 +704,11 @@
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Example: "AI Engineer 3 – Portfolio (All Domains) Learning Systems". Sets org-wide content and curriculum strategy. Owns EdTech infrastructure evolution, GenAI content pipelines, and cross-product technical roadmap.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Shapes org-tracker rows and cross-domain standards; portfolio spans teams — reads through §5 department KPIs and org KRAs, not one team view.</t>
         </is>
@@ -674,13 +716,274 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0E6E5C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>v3 progression machinery — the production principle, the A1–A4 Agent Scope scale, promotion gates, and stay bars. Becomes the standing Progression Policy document when formalized.</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Production principle</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>All content production runs through agents — humans design, review, and improve the systems that produce. Named exception, so the claim stays honest: the video production pipeline (recording, editing, review) — agenticity not required there. This principle is what makes the first two rungs' job descriptions true, and it turns Agentic Production Coverage from a metric into a mandate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Agent Scope</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>A1 — Operate</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Run an existing agent pipeline: review outputs, tune prompts, handle escalations; keep accuracy and cost inside budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>A2 — Improve</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Move an agent's numbers: evals, retrieval quality, unit-cost reduction — with a before/after you can show.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>A3 — Build</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Design and ship a new content agent end-to-end whose impact holds in the metrics. AI Engineer bar: at least 2–3 built and adopted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>A4 — Orchestrate</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Systems of agents carrying production: multi-agent workflows, escalation design (when agents act alone, when they hand to humans), agents other people run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Role mapping</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Intern converts having shown A1 + A2 · AI Engineer reaches A3 within the year · Senior operates at A4 (the leverage route) · Lead runs the team's agent fleet through people · AI Engineer 3 sets the org's agent architecture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Promotion gate</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Requirements (all of them)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="119" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Conversion gate — Associate AI Engineer → AI Engineer, at 6 months</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>1. Runs assigned agent pipelines end-to-end without supervision — prompts tuned, outputs reviewed, escalations handled (A1–A2 shown).
+2. Judgment demonstrated: their sample reviews agree with expert reviews (gold-standard comparisons, eval passes) — they can tell good output from plausible output.
+3. Domain floor: has produced representative content items manually during the ramp — you can't review what you can't do.
+4. Decided by: supervising Senior / AI Engineer Lead proposes with ramp evidence; HOD confirms. Package set by HR at conversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="145" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>AI Engineer → Senior AI Engineer — the 2× bar</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>1. Surface ≈ 2× an AI Engineer's — courses × complexity, any mix of depth, breadth, or leverage (A4 agent systems are the leverage route).
+2. Quality held: all their Section B rows at budget, 2+ consecutive cycles.
+3. Leverage visible: Agentic Production Coverage contribution plus falling cost rows for their courses.
+4. People growing: mentorship evidence (Power Performers Created) — guiding work, not owning ratings.
+5. AI Engineer Lead proposes with row evidence; HOD + calibration confirm. Minimum 1 year in role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="145" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer → AI Engineer Lead — people outcomes define the title</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>1. A Lead seat exists — the span rule creates them: ~5–8 members per Lead (number with HR).
+2. Already answering beyond their slice: full-Section-B literacy shown at reviews, Section A lane awareness.
+3. People outcomes proven as a mentor: retention and growth of the people they guided.
+4. Accepts the accountability that defines the title: ratings, retention, growth and hiring for members.
+5. HOD + PM-head calibration confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="93" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>AI Engineer Lead → AI Engineer 3 — the org seat</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1. Org-level surface already held: org-tracker rows shaped, cross-domain standards authored and adopted.
+2. Their team runs without them day to day — the bus-factor test, passed.
+3. By org need, not tenure. HOD proposes; founders / PM-head calibration confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Holding the role (the stay bar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Associate AI Engineer (internship)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Ramp evidence accumulating on schedule — A1 shown, then A2, inside the 6 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="78" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Their modules' Section B rows at budget each cycle — velocity, quality, issue-recurrence, and the cost rows for their courses.
+Agent scope advancing: by year-end, 2–3 content agents built and adopted, impact visible in Agentic Production Coverage or falling cost rows (A3).
+Rating floor: Performance + Role Competence pillars in band. Two consecutive cycles below budget → a structured gap conversation with their Lead: what's missing, the plan, the timeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>The 2× surface stays held at budget — Senior isn't a medal, it's a load. The slice doesn't quietly shrink.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>AI Engineer Lead</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>The team's full Section B in band, plus the people outcomes — retention, Power Performers Created — read by the rating framework as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>AI Engineer 3</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>The standards they authored still adopted and alive; places the org's learning-systems bets — defines what “proven to work” means across domains.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
@@ -701,7 +1004,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>21 progression areas × 4 levels — verbatim from source. AI Engineer 3 sits above Lead (org-wide scope); the matrix deliberately stops at Lead.</t>
+          <t>21 progression areas × 4 levels — verbatim from source except rows marked ▲ (rewritten agent-first in v3). AI Engineer 3 sits above Lead (org-wide scope); the matrix deliberately stops at Lead.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -723,17 +1026,17 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>Associate AI Engineer (Intern)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer 1</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer 2</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -966,7 +1269,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
@@ -974,31 +1277,31 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Production Systems</t>
+          <t>Production Systems ▲</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Uses assigned tools with guidance</t>
+          <t>Manages and improves the agents they run: accuracy, retrieval quality, cost metrics held inside budget (A1–A2).</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Masters content production tools and workflows</t>
+          <t>Builds new content agents end-to-end — at least 2–3 built and adopted, impact visible in the metrics (A3).</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Optimizes production systems for efficiency</t>
+          <t>Orchestrates systems of agents carrying production: multi-agent workflows, escalation design, agents other people run (A4).</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Evaluates and selects production systems</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
+          <t>Runs the team's agent fleet through people: fleet health, standards, and the coverage number answered for at review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
@@ -1006,27 +1309,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Learning Systems Design</t>
+          <t>Learning Systems Design ▲</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Creates basic assessments with guidance</t>
+          <t>Sees how learning is measured up close: item stats, quiz score bands, eval outcomes for the modules they support.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Manages component mix (MCQs, coding, projects). Selects learning environments</t>
+          <t>Instruments their own modules: formative and summative signals watched, weak items found and fixed, learning deltas shown.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Owns component strategy. Optimizes learning environments (playgrounds, cloud IDEs, GenAI)</t>
+          <t>Invents new ways to teach that take advantage of agentic AI — and applies rigorous measurement to prove users are developing new skills and retaining them. Raises the EEC / DCD asks from the SME seat.</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Strategic ownership across portfolio. Integrates support systems (AI tutor, analytics)</t>
+          <t>Makes invention repeatable: eval environments and capability delivery answered for, measurement standards set for the team.</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
@@ -1441,7 +1744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Progression area → named KPI rows (tracker / FullStack &amp; CS Core team view). The v2 addition: every area now cites live rows, or says why it deliberately has none.</t>
+          <t>Progression area → named KPI rows (tracker / FullStack &amp; CS Core team view). v2 wired every area to live rows (or said why not, by design); v3 adds the Learning Systems Design measurement reads.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1492,7 +1795,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="39" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Foundation</t>
@@ -1510,7 +1813,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Read through interfaces: team-view Section C asks raised and honoured, §7 counterparty standing.</t>
+          <t>Review evidence — influence is work adopted beyond your lane: SOPs and agents other teams run, team-view Section C asks raised → accepted → delivered, §7 counterparty standing.</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1828,7 @@
           <t>Content Quality</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate · Module-Quiz Score Bands</t>
         </is>
@@ -1547,7 +1850,7 @@
           <t>Content Effectiveness</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Learner Accessed Content Completion Rate · Practice Attempt-to-Completion Rate · Engagement-Matrix Cell Migration · Summative + Formative Achievement</t>
         </is>
@@ -1569,7 +1872,7 @@
           <t>Curriculum Design</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Pedagogy Initiative Impact · University Curriculum Compliance</t>
         </is>
@@ -1591,7 +1894,7 @@
           <t>Content Velocity</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Learning Content Hours Delivered · Vernacular Content Hours Delivered · Practice &amp; Assessment Content Pieces Delivered</t>
         </is>
@@ -1613,7 +1916,7 @@
           <t>Industry Upgrades</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Industry Update Adherence · Tech Stack Freshness Rate</t>
         </is>
@@ -1624,7 +1927,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="65" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
@@ -1635,18 +1938,18 @@
           <t>Production Systems</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Agentic Production Coverage</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Publishing through ACP pipelines; cost rows below read the efficiency it buys.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
+          <t>Publishing through ACP pipelines; cost rows below read the efficiency it buys. The Agent Scope scale grades the work — operate and improve (A1–A2), build (A3), orchestrate (A4); agent-ops observability lives here: the day starts and ends in the pipeline dashboards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
@@ -1657,18 +1960,18 @@
           <t>Learning Systems Design</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Evaluation Environment Coverage · Domain Capability Delivery</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Evaluation Environment Coverage · Domain Capability Delivery · Summative + Formative Achievement · Module-Quiz Score Bands</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>The Domain Product Enablement pair — raised/accepted by SMEs, built by PMs + Engineering, accountability in Learning Domains. Reads: Learning Environment Satisfaction, PAtC env-friction leg.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>The Domain Product Enablement pair — raised/accepted by SMEs, built by PMs + Engineering, accountability in Learning Domains — plus the v3 measurement proof: achievement and quiz-band reads shared with Content Effectiveness / Content Quality (the APC double-read precedent). Also reads: Learning Environment Satisfaction, PAtC env-friction leg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
@@ -1679,14 +1982,14 @@
           <t>GenAI Orchestration &amp; Content Automation</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Agentic Production Coverage · Cost per MCQ Generated · Cost per Coding Question</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Mandatory from AI Engineer 1 — orchestration shows up as coverage plus falling unit costs.</t>
+          <t>Mandatory from day one — the internship runs on it. Orchestration shows up as coverage plus falling unit costs; prompt craftsmanship and AI operational literacy are named expectations here.</t>
         </is>
       </c>
     </row>
@@ -1701,7 +2004,7 @@
           <t>Business Impact</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Summative Skill Assessment Achievement Rate · Formative Skill Assessment Achievement Rate · Graded Assessment Achievement Rate (NIAT) · Weekly Active Users (Launchpad)</t>
         </is>
@@ -1745,7 +2048,7 @@
           <t>Execution</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate · Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -1822,7 +2125,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
+    <row r="19" ht="39" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
@@ -1833,14 +2136,14 @@
           <t>Best Practices</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Cost of Operations · Creative Resource Utilisation Rate</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Hygiene guardrails from the Team Ops &amp; People block — run by the team's PM; no org ladder by design.</t>
+          <t>Hygiene guardrails from the Team Ops &amp; People block — run by the team's PM; no org ladder by design. SOPs runnable by others are the review evidence — the bus-factor guard.</t>
         </is>
       </c>
     </row>
@@ -1855,7 +2158,7 @@
           <t>Cross-Functionality</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate</t>
         </is>
@@ -1877,7 +2180,7 @@
           <t>Stakeholder Collaboration</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -1921,7 +2224,7 @@
           <t>Mentorship</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Power Performers Created</t>
         </is>
@@ -1940,7 +2243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
@@ -2004,7 +2307,7 @@
           <t>Assessment score improvements, competency progression</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Summative + Formative Skill Assessment Achievement · org KRA 1 SPI Score Bands</t>
         </is>
@@ -2026,7 +2329,7 @@
           <t>Issues resolved within SLA, quality of implementation</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate</t>
         </is>
@@ -2048,7 +2351,7 @@
           <t>Planned updates on schedule, emerging skills coverage</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Industry Update Adherence · Tech Stack Freshness Rate</t>
         </is>
@@ -2070,7 +2373,7 @@
           <t>Concept understanding improvements, completion rates, delivery innovation</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Pedagogy Initiative Impact · Agentic Production Coverage</t>
         </is>
@@ -2114,7 +2417,7 @@
           <t>Pedagogical excellence, content coherence, engagement quality</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Content Issue Recurrence Rate · Module-Quiz Score Bands · Engagement-Matrix Cell Migration</t>
         </is>
@@ -2136,7 +2439,7 @@
           <t>Effective use of AI for content production, quality of automation systems, cost/velocity optimization through AI, team GenAI capability development</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Agentic Production Coverage</t>
         </is>
@@ -2158,7 +2461,7 @@
           <t>Cost per learning hour, cost per assessment, resource optimization</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Cost per Learning Hour · Cost per MCQ · Cost per Coding Question</t>
         </is>
@@ -2180,7 +2483,7 @@
           <t>Monthly content hours delivery, practice/assessment production</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Learning Content Hours Delivered · Practice &amp; Assessment Content Pieces Delivered</t>
         </is>
@@ -2202,7 +2505,7 @@
           <t>Request fulfillment within timeframes, stakeholder satisfaction</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate · Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -2246,7 +2549,7 @@
           <t>Members ready for next level, training program design</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Power Performers Created</t>
         </is>
@@ -2290,7 +2593,7 @@
           <t>Active participation, candidate evaluation quality, new hire success rate</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Hires Made · Cost per Hire</t>
         </is>
@@ -2312,7 +2615,7 @@
           <t>High potential recognition, development opportunities, succession planning</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Team Retention Rate</t>
         </is>
@@ -2601,14 +2904,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2637,17 +2940,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>Associate AI Engineer (Intern)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer 1</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer 2</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2872,505 +3175,518 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>v3 note</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>After the merge, the old level-1 column calibrates entry into the AI Engineer band; the old level-2 column calibrates the Senior bar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Complexity</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Domains</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Why It Matters</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Low (1.0x)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>English, Aptitude, Mathematics</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Stable content, fewer dependencies, straightforward pedagogy</t>
-        </is>
-      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Medium (1.5x)</t>
+          <t>Low (1.0x)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>CS Core, DevOps, Programming</t>
+          <t>English, Aptitude, Mathematics</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Moderate evolution, standard dependencies, regular updates</t>
+          <t>Stable content, fewer dependencies, straightforward pedagogy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>High (2.0x)</t>
+          <t>Medium (1.5x)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>FullStack, GenAI</t>
+          <t>CS Core, DevOps, Programming</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Rapid evolution, multiple frameworks, high SME involvement</t>
+          <t>Moderate evolution, standard dependencies, regular updates</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>High (2.0x)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>FullStack, GenAI</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Rapid evolution, multiple frameworks, high SME involvement</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Very High (2.5x)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>System Design, DS&amp;Algo, DS/ML</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Highest evolution rate, specialized tracks, critical for placements</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Intensive Online</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>~3,000</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Flexible, self-paced</t>
-        </is>
-      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Intensive Offline</t>
+          <t>Intensive Online</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>~200</t>
+          <t>~3,000</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Cohort-based, in-person</t>
+          <t>Flexible, self-paced</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Academy</t>
+          <t>Intensive Offline</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>~30,000</t>
+          <t>~200</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Largest reach, 2 years</t>
+          <t>Cohort-based, in-person</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>NIAT</t>
+          <t>Academy</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>~8,500</t>
+          <t>~30,000</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>University partnerships (2024-2025)</t>
+          <t>Largest reach, 2 years</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>NIAT</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>~8,500</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>University partnerships (2024-2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>Launchpad</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>~300</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Specialized entry program</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Key Tracks</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Programming</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Python (60), JS (35), Java (30)</t>
-        </is>
-      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>DS &amp; Algorithms</t>
+          <t>Programming</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Fundamentals (80), Advanced (80), Problem Solving (80)</t>
+          <t>Python (60), JS (35), Java (30)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>DS &amp; Algorithms</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>MERN (120), Django (30), SpringBoot (30)</t>
+          <t>Fundamentals (80), Advanced (80), Problem Solving (80)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>CS Core</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Database (35), OS (35), Networks (35), Linux (10)</t>
+          <t>MERN (120), Django (30), SpringBoot (30)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>DS &amp; ML</t>
+          <t>CS Core</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Foundations (25), ML (25), Deep Learning (75), Production (30), Advanced GenAI (40)</t>
+          <t>Database (35), OS (35), Networks (35), Linux (10)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>DS &amp; ML</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Intro (30), Building LLMs (30), Projects (30)</t>
+          <t>Foundations (25), ML (25), Deep Learning (75), Production (30), Advanced GenAI (40)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>System Design</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>High-Level (30), Low-Level (30)</t>
+          <t>Intro (30), Building LLMs (30), Projects (30)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>System Design</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Probability &amp; Stats (25), Linear Algebra (25)</t>
+          <t>High-Level (30), Low-Level (30)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Aptitude</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Quant (30), Numerical (30), Logical (30), Advanced (30)</t>
+          <t>Probability &amp; Stats (25), Linear Algebra (25)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Aptitude</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Foundation (15), Advanced (15), Applied (15), Analytics (15)</t>
+          <t>Quant (30), Numerical (30), Logical (30), Advanced (30)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Foundation (15), Advanced (15), Applied (15), Analytics (15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t>DevOps &amp; Testing</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Cloud Foundations (30), Selenium (30)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>2026 doc term</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>In the KPI system</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Functions</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>§10 embedded functions + the content domain teams. “Packaging Teams” = Content Systems &amp; Infra teams (Pavan, Aug 2026).</t>
-        </is>
-      </c>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Stakeholders</t>
+          <t>Functions</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>§7 counterparties — reached through team-view Section C asks, never staffed into lanes.</t>
+          <t>§10 embedded functions + the content domain teams. “Packaging Teams” = Content Systems &amp; Infra teams (Pavan, Aug 2026).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Stakeholders</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Unchanged — Founders, HODs.</t>
+          <t>§7 counterparties — reached through team-view Section C asks, never staffed into lanes.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Peer Content Teams</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>The other §10 sub-departments (domain teams).</t>
+          <t>Unchanged — Founders, HODs.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t>Peer Content Teams</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>The other §10 sub-departments (domain teams).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>Support Teams</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Unchanged — HR, Finance, L&amp;D, Facilities.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>“Owns” / P&amp;L language</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Translated to the axis rule: Lane (col L) = accountability · Functions (col K) = who works. A Lead answers for the team's Section B; lane numbers stay with lane leads.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="B45:E45"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B39:E39"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B11:E11"/>
     <mergeCell ref="B42:E42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
@@ -3436,7 +3752,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>The team's AI Engineer Lead. KPIs cascade Lead → PM: the Lead answers for the numbers at review; the PM runs them day to day.</t>
+          <t>The team's AI Engineer Lead. KPIs cascade Lead → PM: the Lead answers for the numbers at review; the PM runs them day to day. Team shape guardrail: ~5–8 makers per Lead (number with HR).</t>
         </is>
       </c>
     </row>

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -45,17 +45,17 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="FF666666"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <color rgb="FF1A1A1A"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
@@ -499,58 +499,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI Engineer Ladder — content-department domain teams · v3 August 2026 (internship rung · AI Engineer 1 + 2 merged · Senior AI Engineer added · descriptors from the March 2026 SDE framework; comp for changed rungs with HR)</t>
+          <t>AI Engineer Ladder — content-department domain teams · August 2026 · five levels: a 6-month internship rung, three employee rungs to Lead, then the org seat. Comp for the changed rungs sits with HR.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Title (v3 pattern)</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Formerly (source)</t>
+          <t>Comp | Tenure</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Comp | Tenure</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Role (v3)</t>
+          <t>Scope (framework descriptor)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Scope (source, examples retitled)</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Metric surface (v3)</t>
+          <t>Metric surface</t>
         </is>
       </c>
     </row>
@@ -562,25 +555,20 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Associate SDE, Learning Systems - [Domain Name]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
           <t>Internship stipend — set by HR | 6-month internship</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>6-month internship — manages agents under supervision from day one: runs existing pipelines, reviews outputs, tunes prompts, handles escalations (A1), then shows measurable improvement on an agent's numbers (A2). Produces representative content items manually during the ramp — the domain floor. Converts through the gate below.</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Example: "Associate AI Engineer – FullStack Learning Systems" or "Associate AI Engineer – GenAI Learning Systems". Creates content with guidance (lessons, exercises, projects, assessments). Learns to integrate code playgrounds, evaluation judges, and learning platforms. Handles 0.5-1 domain, 40-100 content hours, reaches 2K-5K students.</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Contributes on sample surfaces along the internship ramp — no rows answered for; growth is read through ramp evidence (A1→A2 on the Agent Scope scale).</t>
         </is>
@@ -594,27 +582,22 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>SDE 1, Learning Systems - [Domain]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>9–24L, band under HR review (spans the two merged bands) | ≥1 year in role before Senior eligibility</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Manages agents. Owns modules end-to-end and builds new content agents — 2–3 built and adopted by year-end, impact visible in the metrics (A3). One band: the old AI Engineer 1 and 2 merge here.</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+          <t>9–24L, band under HR review (the full IC span) | ≥1 year in role before Senior eligibility</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Manages agents. Owns modules end-to-end and builds new content agents — 2–3 built and adopted by year-end, impact visible in the metrics (A3). One band, covering the full individual-contributor span before Senior.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Example: "AI Engineer – DS/ML Learning Systems". Creates domain content independently (lessons, exercises, projects). Engineers learning systems by selecting appropriate platforms (IDEs, cloud environments, assessment engines). Owns 1-2 domains. Manages 100-250 hours, reaches 5K-10K students.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Answers for the Section B velocity + quality rows of the modules they own (their content hours, pieces, issue-recurrence share) — with 2–3 content agents built and adopted (A3).</t>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Answers for the Section B velocity + quality rows of the modules they own (their content hours, pieces, issue-recurrence share) — a topic surface of ≈ 100 topics at FullStack / GenAI complexity, refreshed every 6 months, with 2–3 content agents built and adopted (A3).</t>
         </is>
       </c>
     </row>
@@ -626,27 +609,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SDE 2, Learning Systems - [Domain Portfolio]</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
           <t>Band under HR review — new rung | reached through the 2× gate below</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Manages agent systems and mentors humans — the force-multiplier rung. Holds ≈2× an AI Engineer's complexity-weighted surface by depth, breadth, or leverage; orchestrating systems of agents (A4) is the leverage route. Invents new ways to teach with agentic AI and proves them with rigorous measurement.</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Example: "Senior AI Engineer – FullStack, System Design &amp; CS Core Learning Systems". Leads content creation across multiple domains. Architects platform systems and optimizes evaluation pipelines. Manages 2-5 team members across 3-4 domains. Manages 250-450 hours, reaches 10K-20K students.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Answers for a domain slice ≈ 2× an AI Engineer's complexity-weighted surface — by depth, breadth, or leverage (A4 agent systems); first Section C asks raised in their name.</t>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Answers for a domain slice ≈ 2× an AI Engineer's complexity-weighted topic surface — by depth, breadth, or leverage (A4 agent systems); first Section C asks raised in their name.</t>
         </is>
       </c>
     </row>
@@ -658,25 +636,20 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>SDE Lead, Learning Systems - [Domain Portfolio]</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
           <t>24L to 30L | 5+ years</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Manages humans who manage agents. Runs the team: full Section B answered for at review; people outcomes — ratings, retention, growth, hiring — define the title. Span ~5–8 members (number with HR).</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Example: "AI Engineer Lead – Programming, FullStack, CS Core, DevOps Learning Systems". Owns content strategy and creation across portfolio. Designs platform architecture and GenAI-driven content systems. Leads 15-25 members across 4-6 domains. Manages 450+ hours, reaches 20K-40K+ students.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Answers for the team's full Section B at review and supports the Section A lane numbers; span ~5–8 members; the rating framework below applies as written.</t>
         </is>
@@ -690,25 +663,20 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SDE 3, Learning Systems - [Domain Portfolio]</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
           <t>30L+ | 7+ years</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Example: "AI Engineer 3 – Portfolio (All Domains) Learning Systems". Sets org-wide content and curriculum strategy. Owns EdTech infrastructure evolution, GenAI content pipelines, and cross-product technical roadmap.</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Example: "AI Engineer 3 – Portfolio (All Domains) Learning Systems". Sets org-wide content and curriculum strategy. Owns EdTech infrastructure evolution, GenAI content pipelines, and cross-product technical roadmap.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Shapes org-tracker rows and cross-domain standards; portfolio spans teams — reads through §5 department KPIs and org KRAs, not one team view.</t>
         </is>
@@ -716,7 +684,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -739,7 +707,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>v3 progression machinery — the production principle, the A1–A4 Agent Scope scale, promotion gates, and stay bars. Becomes the standing Progression Policy document when formalized.</t>
+          <t>Progression machinery — the production principle, the A1–A4 Agent Scope scale, promotion gates, and stay bars. Becomes the standing Progression Policy document when formalized.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -750,7 +718,7 @@
           <t>Production principle</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>All content production runs through agents — humans design, review, and improve the systems that produce. Named exception, so the claim stays honest: the video production pipeline (recording, editing, review) — agenticity not required there. This principle is what makes the first two rungs' job descriptions true, and it turns Agentic Production Coverage from a metric into a mandate.</t>
         </is>
@@ -774,7 +742,7 @@
           <t>A1 — Operate</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Run an existing agent pipeline: review outputs, tune prompts, handle escalations; keep accuracy and cost inside budget.</t>
         </is>
@@ -786,7 +754,7 @@
           <t>A2 — Improve</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Move an agent's numbers: evals, retrieval quality, unit-cost reduction — with a before/after you can show.</t>
         </is>
@@ -798,7 +766,7 @@
           <t>A3 — Build</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Design and ship a new content agent end-to-end whose impact holds in the metrics. AI Engineer bar: at least 2–3 built and adopted.</t>
         </is>
@@ -810,19 +778,19 @@
           <t>A4 — Orchestrate</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Systems of agents carrying production: multi-agent workflows, escalation design (when agents act alone, when they hand to humans), agents other people run.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Role mapping</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Intern converts having shown A1 + A2 · AI Engineer reaches A3 within the year · Senior operates at A4 (the leverage route) · Lead runs the team's agent fleet through people · AI Engineer 3 sets the org's agent architecture.</t>
         </is>
@@ -846,7 +814,7 @@
           <t>Conversion gate — Associate AI Engineer → AI Engineer, at 6 months</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>1. Runs assigned agent pipelines end-to-end without supervision — prompts tuned, outputs reviewed, escalations handled (A1–A2 shown).
 2. Judgment demonstrated: their sample reviews agree with expert reviews (gold-standard comparisons, eval passes) — they can tell good output from plausible output.
@@ -861,7 +829,7 @@
           <t>AI Engineer → Senior AI Engineer — the 2× bar</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>1. Surface ≈ 2× an AI Engineer's — courses × complexity, any mix of depth, breadth, or leverage (A4 agent systems are the leverage route).
 2. Quality held: all their Section B rows at budget, 2+ consecutive cycles.
@@ -877,7 +845,7 @@
           <t>Senior AI Engineer → AI Engineer Lead — people outcomes define the title</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>1. A Lead seat exists — the span rule creates them: ~5–8 members per Lead (number with HR).
 2. Already answering beyond their slice: full-Section-B literacy shown at reviews, Section A lane awareness.
@@ -893,7 +861,7 @@
           <t>AI Engineer Lead → AI Engineer 3 — the org seat</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>1. Org-level surface already held: org-tracker rows shaped, cross-domain standards authored and adopted.
 2. Their team runs without them day to day — the bus-factor test, passed.
@@ -919,7 +887,7 @@
           <t>Associate AI Engineer (internship)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Ramp evidence accumulating on schedule — A1 shown, then A2, inside the 6 months.</t>
         </is>
@@ -931,7 +899,7 @@
           <t>AI Engineer</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Their modules' Section B rows at budget each cycle — velocity, quality, issue-recurrence, and the cost rows for their courses.
 Agent scope advancing: by year-end, 2–3 content agents built and adopted, impact visible in Agentic Production Coverage or falling cost rows (A3).
@@ -945,7 +913,7 @@
           <t>Senior AI Engineer</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>The 2× surface stays held at budget — Senior isn't a medal, it's a load. The slice doesn't quietly shrink.</t>
         </is>
@@ -957,7 +925,7 @@
           <t>AI Engineer Lead</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>The team's full Section B in band, plus the people outcomes — retention, Power Performers Created — read by the rating framework as written.</t>
         </is>
@@ -969,7 +937,7 @@
           <t>AI Engineer 3</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>The standards they authored still adopted and alive; places the org's learning-systems bets — defines what “proven to work” means across domains.</t>
         </is>
@@ -1004,7 +972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>21 progression areas × 4 levels — verbatim from source except rows marked ▲ (rewritten agent-first in v3). AI Engineer 3 sits above Lead (org-wide scope); the matrix deliberately stops at Lead.</t>
+          <t>21 progression areas × 4 levels — carried verbatim from the framework except the rows marked ▲ (rewritten agent-first). AI Engineer 3 sits above Lead (org-wide scope); the matrix deliberately stops at Lead.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1046,7 +1014,7 @@
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1056,29 +1024,29 @@
           <t>Scope of Work</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Task-based content creation</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Domain ownership (set of courses)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Multiple domains, product coverage</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Multi-curriculum, product strategy</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1088,29 +1056,29 @@
           <t>Influence</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Individual contributor</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Influences peers, small team</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Influences team, cross-product</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Influences across content teams</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1120,29 +1088,29 @@
           <t>Content Quality</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Follows templates with guidance</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Creates clear, accurate content. Ensures technical accuracy and standards</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Produces quality at scale. Drives QA processes</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Establishes quality standards and frameworks</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1152,29 +1120,29 @@
           <t>Content Effectiveness</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Learns effectiveness basics</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Monitors performance metrics. Applies pedagogy best practices</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Drives pedagogy initiatives. Improves via feedback analysis</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Owns pedagogy R&amp;D. Optimizes effectiveness org-wide</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1184,29 +1152,29 @@
           <t>Curriculum Design</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Follows structure from leads</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Designs course outlines for single domain with guidance</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Architects curriculum across multiple domains. Owns end-to-end journeys</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Owns strategic curriculum design across portfolio</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1216,29 +1184,29 @@
           <t>Content Velocity</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>1 hr session/day (100 MCQs, 6 coding questions, or 2 projects)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>5 hrs/month independently</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>12-20 hrs/month across domains</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>25-50 hrs/month. Manages team velocity</t>
         </is>
       </c>
     </row>
     <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1248,29 +1216,29 @@
           <t>Industry Upgrades</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Receives updates from leads. Implements changes to content/systems as directed</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Keeps domain content, platforms, and software current with industry standards. Updates evaluation systems and tools</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Drives industry alignment across domains. Upgrades learning systems (IDEs, cloud platforms, assessment engines) proactively</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Sets industry standards for portfolio. Ensures entire learning system (content, software, platforms) stays current. Anticipates industry shifts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1280,29 +1248,29 @@
           <t>Production Systems ▲</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Manages and improves the agents they run: accuracy, retrieval quality, cost metrics held inside budget (A1–A2).</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Builds new content agents end-to-end — at least 2–3 built and adopted, impact visible in the metrics (A3).</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Orchestrates systems of agents carrying production: multi-agent workflows, escalation design, agents other people run (A4).</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Runs the team's agent fleet through people: fleet health, standards, and the coverage number answered for at review.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1312,29 +1280,29 @@
           <t>Learning Systems Design ▲</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Sees how learning is measured up close: item stats, quiz score bands, eval outcomes for the modules they support.</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Instruments their own modules: formative and summative signals watched, weak items found and fixed, learning deltas shown.</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Invents new ways to teach that take advantage of agentic AI — and applies rigorous measurement to prove users are developing new skills and retaining them. Raises the EEC / DCD asks from the SME seat.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Makes invention repeatable: eval environments and capability delivery answered for, measurement standards set for the team.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="104" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1344,29 +1312,29 @@
           <t>GenAI Orchestration &amp; Content Automation</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Uses GenAI to accelerate content creation (exercise generation, code examples, explanations). All output reviewed with team lead before publishing. Builds judgment on what AI does well vs. poorly. Learning to write effective prompts</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Creates content specs before prompting (learning objectives, difficulty, concepts to test). Reviews all AI output for technical accuracy and pedagogy. Catches hallucinations. Uses AI for boilerplate while hand-crafting complex sequences. 30-50% velocity increase</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Builds reusable prompt templates for team. Establishes review checklists for AI content. Trains team on when to use AI vs. manual creation. Monitors quality metrics across AI vs. manual content. 50-100% team velocity increase</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Designs content automation pipelines (bulk generation, curriculum scaffolding, item banks). Creates prompt libraries and quality frameworks. Sets AI usage standards: what requires review, what auto-publishes, what never uses AI. Measures cost per content hour and ROI</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1376,29 +1344,29 @@
           <t>Business Impact</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Supports team deliverables</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Improves learning outcomes and efficiency</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Drives multiple initiatives, cost optimization</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Owns P&amp;L, establishes new verticals, manages budget</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1408,29 +1376,29 @@
           <t>Problem Solving</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Solves minor issues within assigned domain. Fixes immediate gaps</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Identifies root causes. Suggests solutions across functions</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Finds root causes for all stakeholders. Drives learning improvements</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Proposes and executes solutions across entire system (short/mid/long term)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1440,29 +1408,29 @@
           <t>Execution</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Executes assigned tasks. Follows workflows with guidance</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Executes end-to-end for domain independently. Coordinates with cross-functional teams</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Drives execution across domains and team. Plans quarterly deliverables</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Drives execution across entire portfolio. Owns strategic planning (quarterly/annual)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1472,29 +1440,29 @@
           <t>Learnability</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Learns new tools with guidance</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Quickly picks up new technologies. Self-directed learning</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Masters new domains rapidly. Teaches others effectively</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Champions learning culture. Adapts strategically. Identifies skill gaps</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1504,29 +1472,29 @@
           <t>Communication</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Communicates clearly within team. Documents work</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Effective with cross-functional teams. Articulates technical decisions</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Communicates with stakeholders. Influences through data</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Strategic communicator to leadership. Presents portfolio strategy</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1536,29 +1504,29 @@
           <t>Ambiguity Handling</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Works with clear requirements</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Handles moderate ambiguity. Seeks input</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Translates vague problems into solutions</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Identifies and scopes new ambiguous problems</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1568,29 +1536,29 @@
           <t>Best Practices</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Follows established practices</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Refines and shares practices</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Establishes new practices</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Defines and mandates org-wide practices</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1600,29 +1568,29 @@
           <t>Cross-Functionality</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Works with design and engineers on tasks</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Collaborates with graphic design, product, engineers, video editors</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Leads cross-functional initiatives with multiple teams</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Drives cross-functional collaboration across content teams</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1632,29 +1600,29 @@
           <t>Stakeholder Collaboration</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Receives requirements from product</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Engages with instructors, success coaches, program managers, sales, assessments</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Aligns content with stakeholder goals (placements, assessments)</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Partners with product leadership on curriculum roadmap</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1664,29 +1632,29 @@
           <t>Cross-Product Work</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Works within single product</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Coordinates with other products (Academy, NIAT, Intensive)</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Ensures content reusability across products</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Optimizes content strategy across all products</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1696,22 +1664,22 @@
           <t>Mentorship</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Receives mentoring from SDE 1+</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Receives mentoring from AI Engineers and above</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Mentors junior content creators</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Develops and mentors emerging leaders</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Builds and develops teams of 15-25 members</t>
         </is>
@@ -1744,7 +1712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Progression area → named KPI rows (tracker / FullStack &amp; CS Core team view). v2 wired every area to live rows (or said why not, by design); v3 adds the Learning Systems Design measurement reads.</t>
+          <t>Progression area → named KPI rows (tracker / FullStack &amp; CS Core team view). Every area cites the rows it moves, or says why it deliberately has none.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1774,7 +1742,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1784,19 +1752,19 @@
           <t>Scope of Work</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Calibration, not a metric — read through the Portfolio Metrics matrix + domain complexity multipliers below.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="39" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1806,19 +1774,19 @@
           <t>Influence</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Review evidence — influence is work adopted beyond your lane: SOPs and agents other teams run, team-view Section C asks raised → accepted → delivered, §7 counterparty standing.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1833,14 +1801,14 @@
           <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate · Module-Quiz Score Bands</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>The Learning Domains quality loop — recurrence is the tell that a fix actually held.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1855,14 +1823,14 @@
           <t>Learner Accessed Content Completion Rate · Practice Attempt-to-Completion Rate · Engagement-Matrix Cell Migration · Summative + Formative Achievement</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Access-conditioned stickiness pair + the matrix — conduction effects stripped by design.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1877,14 +1845,14 @@
           <t>Pedagogy Initiative Impact · University Curriculum Compliance</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>PII is SME-owned (Pedagogy Experts contribute); compliance rows apply on university-facing work.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1899,14 +1867,14 @@
           <t>Learning Content Hours Delivered · Vernacular Content Hours Delivered · Practice &amp; Assessment Content Pieces Delivered</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>The per-level hours ladder in the matrix is the personal share of these team rows.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1921,14 +1889,14 @@
           <t>Industry Update Adherence · Tech Stack Freshness Rate</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Adherence = planned updates land on schedule; freshness = the audit behind relevance.</t>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Adherence = planned updates land on schedule; freshness = the 6-month topic-refresh audit behind relevance. A topic is PPT + recorded session + practice + quiz content (catalogue hours ≈ topic count) and every refresh is planned as a from-scratch rebuild — this row is what makes a rung's surface size arguable.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1943,14 +1911,14 @@
           <t>Agentic Production Coverage</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Publishing through ACP pipelines; cost rows below read the efficiency it buys. The Agent Scope scale grades the work — operate and improve (A1–A2), build (A3), orchestrate (A4); agent-ops observability lives here: the day starts and ends in the pipeline dashboards.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1965,14 +1933,14 @@
           <t>Evaluation Environment Coverage · Domain Capability Delivery · Summative + Formative Achievement · Module-Quiz Score Bands</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>The Domain Product Enablement pair — raised/accepted by SMEs, built by PMs + Engineering, accountability in Learning Domains — plus the v3 measurement proof: achievement and quiz-band reads shared with Content Effectiveness / Content Quality (the APC double-read precedent). Also reads: Learning Environment Satisfaction, PAtC env-friction leg.</t>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>The Domain Product Enablement pair — raised/accepted by SMEs, built by PMs + Engineering, accountability in Learning Domains — plus the measurement proof: achievement and quiz-band reads shared with Content Effectiveness / Content Quality (the APC double-read precedent). Also reads: Learning Environment Satisfaction, PAtC env-friction leg.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1987,14 +1955,14 @@
           <t>Agentic Production Coverage · Cost per MCQ Generated · Cost per Coding Question</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Mandatory from day one — the internship runs on it. Orchestration shows up as coverage plus falling unit costs; prompt craftsmanship and AI operational literacy are named expectations here.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -2009,14 +1977,14 @@
           <t>Summative Skill Assessment Achievement Rate · Formative Skill Assessment Achievement Rate · Graded Assessment Achievement Rate (NIAT) · Weekly Active Users (Launchpad)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>The Section B Business Impact block; ladders to org KRAs 1, 4 and 5.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2026,19 +1994,19 @@
           <t>Problem Solving</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Review evidence — no direct KPI by design.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2053,14 +2021,14 @@
           <t>Cross-functional Sprint Delivery Rate · Stakeholder Content Request Fulfillment Rate</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Committed-vs-delivered is the execution read.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2070,19 +2038,19 @@
           <t>Learnability</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Review evidence — GenAI adoption surfaces indirectly in Agentic Production Coverage contribution.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2092,19 +2060,19 @@
           <t>Communication</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Review evidence — no direct KPI by design.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2114,19 +2082,19 @@
           <t>Ambiguity Handling</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Review evidence — no direct KPI by design.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2141,14 +2109,14 @@
           <t>Cost of Operations · Creative Resource Utilisation Rate</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Hygiene guardrails from the Team Ops &amp; People block — run by the team's PM; no org ladder by design. SOPs runnable by others are the review evidence — the bus-factor guard.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2163,14 +2131,14 @@
           <t>Cross-functional Sprint Delivery Rate</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Plus the health of Section C asks the person is party to.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2185,14 +2153,14 @@
           <t>Stakeholder Content Request Fulfillment Rate</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Ladders to dept Stakeholder Alignment (§5).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2202,19 +2170,19 @@
           <t>Cross-Product Work</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Read through the Product column — Section B rows carried per product (NIAT · Academy · Launchpad slots).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2229,7 +2197,7 @@
           <t>Power Performers Created</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Rating Pillar 3 (Develop the Best) — first direct read: members made next-level-ready, counted per appraisal cycle. Feedback quality and growth opportunities stay review-based.</t>
         </is>
@@ -2297,12 +2265,12 @@
           <t>Impact on Learning Outcomes</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Assessment score improvements, competency progression</t>
         </is>
@@ -2319,12 +2287,12 @@
           <t>Feedback Resolution</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Issues resolved within SLA, quality of implementation</t>
         </is>
@@ -2341,12 +2309,12 @@
           <t>Industry Upgrades</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Planned updates on schedule, emerging skills coverage</t>
         </is>
@@ -2363,12 +2331,12 @@
           <t>Pedagogy/R&amp;D</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Concept understanding improvements, completion rates, delivery innovation</t>
         </is>
@@ -2407,12 +2375,12 @@
           <t>Curriculum Quality</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Pedagogical excellence, content coherence, engagement quality</t>
         </is>
@@ -2429,12 +2397,12 @@
           <t>GenAI Orchestration &amp; Automation</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Effective use of AI for content production, quality of automation systems, cost/velocity optimization through AI, team GenAI capability development</t>
         </is>
@@ -2451,12 +2419,12 @@
           <t>Cost Efficiency</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Cost per learning hour, cost per assessment, resource optimization</t>
         </is>
@@ -2473,12 +2441,12 @@
           <t>Content Velocity</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Monthly content hours delivery, practice/assessment production</t>
         </is>
@@ -2495,12 +2463,12 @@
           <t>Cross-functional Collaboration</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Request fulfillment within timeframes, stakeholder satisfaction</t>
         </is>
@@ -2539,12 +2507,12 @@
           <t>Power Performers Created</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Members ready for next level, training program design</t>
         </is>
@@ -2561,17 +2529,17 @@
           <t>Timely Feedback</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Regular 1-on-1s, actionable feedback, development plan clarity</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2583,12 +2551,12 @@
           <t>Hiring</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Active participation, candidate evaluation quality, new hire success rate</t>
         </is>
@@ -2605,12 +2573,12 @@
           <t>Talent Nurturing</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>High potential recognition, development opportunities, succession planning</t>
         </is>
@@ -2627,17 +2595,17 @@
           <t>Growth Opportunities</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Stretch assignments, cross-functional exposure, leadership development</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2671,17 +2639,17 @@
           <t>Framework Adherence</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Following org processes, execution consistency</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2693,17 +2661,17 @@
           <t>Learning Culture</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Conducting learning hours, knowledge sharing, skill development</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2715,17 +2683,17 @@
           <t>Outcome Over Output</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Business impact focus vs. volume, quality over quantity</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2737,17 +2705,17 @@
           <t>Growth Mindset</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Staying current with trends, learning from new tech, embracing change</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2759,17 +2727,17 @@
           <t>Mission Alignment</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Living company values, brand protection, mission-driven decisions</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2781,7 +2749,7 @@
           <t>Calculation</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Calculation: Final Rating = (Performance × 0.50) + (Competence × 0.25) + (Develop Best × 0.15) + (Culture × 0.10)</t>
         </is>
@@ -2806,94 +2774,94 @@
       <c r="D27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Exceptional</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Exceeded significantly</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Exceeds</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Above expectations</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Meets</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>As expected (target)</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Needs Improvement</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Struggled to meet</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Unsatisfactory</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Failed to meet</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2965,22 +2933,22 @@
           <t>Experience</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>1-3+ years</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>3+ years</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>5+ years</t>
         </is>
@@ -2992,22 +2960,22 @@
           <t>Domains</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>0.5-1</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>3-4</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>4-6</t>
         </is>
@@ -3019,22 +2987,22 @@
           <t>Tracks</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>3-5+</t>
         </is>
@@ -3046,22 +3014,22 @@
           <t>Content Hours</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>40-100</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>100-250</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>250-450</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>450+</t>
         </is>
@@ -3073,22 +3041,22 @@
           <t>Team Size</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Solo (0)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>0-2</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2-5</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>15-25</t>
         </is>
@@ -3100,22 +3068,22 @@
           <t>Student Reach</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>2K-5K</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>5K-10K</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>10K-20K</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>20K-40K+</t>
         </is>
@@ -3127,22 +3095,22 @@
           <t>Products</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
@@ -3154,36 +3122,36 @@
           <t>Key Focus</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Task execution</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Domain ownership</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Team leadership</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Portfolio management</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>v3 note</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>After the merge, the old level-1 column calibrates entry into the AI Engineer band; the old level-2 column calibrates the Senior bar.</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>The AI Engineer column calibrates entry into the band; the Senior column is the 2× bar expressed in portfolio terms.</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3180,12 @@
           <t>Low (1.0x)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>English, Aptitude, Mathematics</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Stable content, fewer dependencies, straightforward pedagogy</t>
         </is>
@@ -3229,12 +3197,12 @@
           <t>Medium (1.5x)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>CS Core, DevOps, Programming</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Moderate evolution, standard dependencies, regular updates</t>
         </is>
@@ -3246,12 +3214,12 @@
           <t>High (2.0x)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>FullStack, GenAI</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Rapid evolution, multiple frameworks, high SME involvement</t>
         </is>
@@ -3263,12 +3231,12 @@
           <t>Very High (2.5x)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>System Design, DS&amp;Algo, DS/ML</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Highest evolution rate, specialized tracks, critical for placements</t>
         </is>
@@ -3299,12 +3267,12 @@
           <t>Intensive Online</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>~3,000</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Flexible, self-paced</t>
         </is>
@@ -3316,12 +3284,12 @@
           <t>Intensive Offline</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>~200</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Cohort-based, in-person</t>
         </is>
@@ -3333,12 +3301,12 @@
           <t>Academy</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>~30,000</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Largest reach, 2 years</t>
         </is>
@@ -3350,12 +3318,12 @@
           <t>NIAT</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>~8,500</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>University partnerships (2024-2025)</t>
         </is>
@@ -3367,12 +3335,12 @@
           <t>Launchpad</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>~300</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Specialized entry program</t>
         </is>
@@ -3403,12 +3371,12 @@
           <t>Programming</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Python (60), JS (35), Java (30)</t>
         </is>
@@ -3420,12 +3388,12 @@
           <t>DS &amp; Algorithms</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Fundamentals (80), Advanced (80), Problem Solving (80)</t>
         </is>
@@ -3437,12 +3405,12 @@
           <t>Full Stack</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>MERN (120), Django (30), SpringBoot (30)</t>
         </is>
@@ -3454,12 +3422,12 @@
           <t>CS Core</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Database (35), OS (35), Networks (35), Linux (10)</t>
         </is>
@@ -3471,12 +3439,12 @@
           <t>DS &amp; ML</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>295</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Foundations (25), ML (25), Deep Learning (75), Production (30), Advanced GenAI (40)</t>
         </is>
@@ -3488,12 +3456,12 @@
           <t>Generative AI</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Intro (30), Building LLMs (30), Projects (30)</t>
         </is>
@@ -3505,12 +3473,12 @@
           <t>System Design</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>High-Level (30), Low-Level (30)</t>
         </is>
@@ -3522,12 +3490,12 @@
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Probability &amp; Stats (25), Linear Algebra (25)</t>
         </is>
@@ -3539,12 +3507,12 @@
           <t>Aptitude</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Quant (30), Numerical (30), Logical (30), Advanced (30)</t>
         </is>
@@ -3556,12 +3524,12 @@
           <t>English</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Foundation (15), Advanced (15), Applied (15), Analytics (15)</t>
         </is>
@@ -3573,12 +3541,12 @@
           <t>DevOps &amp; Testing</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Cloud Foundations (30), Selenium (30)</t>
         </is>
@@ -3605,7 +3573,7 @@
           <t>Functions</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>§10 embedded functions + the content domain teams. “Packaging Teams” = Content Systems &amp; Infra teams (Pavan, Aug 2026).</t>
         </is>
@@ -3617,7 +3585,7 @@
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>§7 counterparties — reached through team-view Section C asks, never staffed into lanes.</t>
         </is>
@@ -3629,7 +3597,7 @@
           <t>Leadership</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Unchanged — Founders, HODs.</t>
         </is>
@@ -3641,7 +3609,7 @@
           <t>Peer Content Teams</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>The other §10 sub-departments (domain teams).</t>
         </is>
@@ -3653,7 +3621,7 @@
           <t>Support Teams</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Unchanged — HR, Finance, L&amp;D, Facilities.</t>
         </is>
@@ -3665,7 +3633,7 @@
           <t>“Owns” / P&amp;L language</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Translated to the axis rule: Lane (col L) = accountability · Functions (col K) = who works. A Lead answers for the team's Section B; lane numbers stay with lane leads.</t>
         </is>
@@ -3726,7 +3694,7 @@
           <t>Title pattern</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Project Manager – [Domain] Learning Systems</t>
         </is>
@@ -3738,7 +3706,7 @@
           <t>Pilot instance</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Project Manager – FullStack &amp; CS Core Learning Systems</t>
         </is>
@@ -3750,7 +3718,7 @@
           <t>Reports to</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>The team's AI Engineer Lead. KPIs cascade Lead → PM: the Lead answers for the numbers at review; the PM runs them day to day. Team shape guardrail: ~5–8 makers per Lead (number with HR).</t>
         </is>
@@ -3762,7 +3730,7 @@
           <t>Comp</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Band pending — defined with HR when the seat is staffed.</t>
         </is>
@@ -3774,7 +3742,7 @@
           <t>Owns (metric surface)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Cost of Operations · Roadmap Items Completion · Hires Made · Cost per Hire · Team Retention Rate · Power Performers Created · Creative Resource Utilisation Rate. The Team Ops &amp; People block of the team view — the FullStack &amp; CS Core pilot carries all 7 (CSI: 6, without the creative-utilisation row). Three of these are also the Lead's Develop-the-Best rating reads: the PM operates the rows, the Lead answers for them.</t>
         </is>
@@ -3786,7 +3754,7 @@
           <t>Interfaces</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Content–Central PMO: the PM feeds the monthly check-in — complete worklogs and current ClickUp statuses are what the PMO's Worklog &amp; Status Hygiene — All Units read counts. Worklog capture is the load-bearing activity: it makes deliverable costing computable.</t>
         </is>
@@ -3798,7 +3766,7 @@
           <t>Progression / rating</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Progression and rating for the PM seat itself: not designed yet — this card fixes the seat, the reporting line and the metric surface first.</t>
         </is>
@@ -3817,132 +3785,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Monthly manager–reportee one-on-ones</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Scheduling roadmap review meetings + Head approval</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Day-to-day ops — standups, learning hours</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Scheduling monthly check-in meets &amp; documenting them in the right place</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Maintaining team assets (laptops, systems)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Ensuring ClickUp adoption</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Keeping deliverable statuses up to date</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Monthly worklog capture → deliverable costs computed for the check-in</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Generating newsletters monthly</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Conducting team outings</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Conducting cycle-wise appraisal meetings</t>
         </is>

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +51,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
@@ -109,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -131,6 +137,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -697,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -817,7 +826,7 @@
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>1. Runs assigned agent pipelines end-to-end without supervision — prompts tuned, outputs reviewed, escalations handled (A1–A2 shown).
-2. Judgment demonstrated: their sample reviews agree with expert reviews (gold-standard comparisons, eval passes) — they can tell good output from plausible output.
+2. Judgment demonstrated: the responsible reviewer — their mentoring AI Engineer or Senior — confirms the intern's reviews catch what their own review would catch, sampled on real work through the ramp; they can tell good output from plausible output.
 3. Domain floor: has produced representative content items manually during the ramp — you can't review what you can't do.
 4. Decided by: supervising Senior / AI Engineer Lead proposes with ramp evidence; HOD confirms. Package set by HR at conversion.</t>
         </is>
@@ -881,65 +890,119 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>One rule</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>The gates say how you climb; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Associate AI Engineer (internship)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Ramp evidence accumulating on schedule — A1 shown, then A2, inside the 6 months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="78" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>The readiness scorecard filling on schedule: A1 shown (assigned pipelines run unsupervised), then A2 (a documented before/after on an agent's accuracy, retrieval quality or unit cost) — never more than one month behind the ramp plan across the six.
+Governance from day one: issue recurrence ≤ 2% on their items · unit costs inside the cost bars on their pipelines (≤ ₹3 an objective practice item; coding questions on the domain scale below) · worklogs complete, statuses current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="146" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>AI Engineer</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Their modules' Section B rows at budget each cycle — velocity, quality, issue-recurrence, and the cost rows for their courses.
-Agent scope advancing: by year-end, 2–3 content agents built and adopted, impact visible in Agentic Production Coverage or falling cost rows (A3).
-Rating floor: Performance + Role Competence pillars in band. Two consecutive cycles below budget → a structured gap conversation with their Lead: what's missing, the plan, the timeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>The four output rows at budget each cycle: Tech Stack Freshness Rate 100% on their ≈ 200 CWT surface (≈ 100 topics at FullStack / GenAI complexity, double on lighter domains) · their CWT share of the team's Learning Content Hours + Practice &amp; Assessment Pieces · Agentic Production Coverage 90% · Summative 35% + Formative 23% on their modules.
+2–3 content agents built and adopted (A3) by year-end — mandatory for the rung, not just scored.
+The four governance rows never breached: issue resolution 80% inside the 2-day TAT · recurrence ≤ 2% · unit costs at budget (≤ ₹10,000 a learning hour · ≤ ₹3 an objective practice item — FIB, MCQ, MMCQ, any type · coding questions under ₹100, scaled by domain below) · sprint delivery 100% + stakeholder fulfillment 90%. A breach zeroes that slice and blocks eligibility for the cycle.
+Rating floor: Performance + Role Competence pillars in band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Senior AI Engineer</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>The 2× surface stays held at budget — Senior isn't a medal, it's a load. The slice doesn't quietly shrink.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>The ≈ 400 CWT surface (2× an AI Engineer, complexity-weighted) held at budget — Senior isn't a medal, it's a load; the slice doesn't quietly shrink.
+A4 live: production coverage attributable to multi-agent systems they own · all their Section B rows at budget 2+ consecutive cycles · unit costs at or below budget, and falling.
+Mentorship on record: ≥ 1 power performer contributed in the trailing 12 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>AI Engineer Lead</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>The team's full Section B in band, plus the people outcomes — retention, Power Performers Created — read by the rating framework as written.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>The team's owned rows at budget at review — ≥ 85% of them (FS pilot: 29 rows) ⚑ — with team Freshness at 100% and team production coverage at 90%, run through people, not personally.
+Business impact at budget on the team's domains: Summative 35% · Formative 23% · SPI band contribution.
+People outcomes as governance: Team Retention ≥ 90% trailing 12 months · ≥ 1 Power Performer created per appraisal cycle · Cost of Operations at plan + Roadmap ≥ 90% (run by the team's PM, answered for by the Lead) · stakeholder 90% + sprint 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>AI Engineer 3</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>The standards they authored still adopted and alive; places the org's learning-systems bets — defines what “proven to work” means across domains.</t>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Reads through department KPIs and org KRAs, not one team view — the bar stays directional until those budgets land: the standards they authored still adopted and alive · portfolio Section B healthy across teams · a Lead bench ready behind them · places the org's learning-systems bets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Low-refresh domains (English, Aptitude, Mathematics, Programming, CS Core, DS &amp; Algo, DevOps, System Design) run the same bar with two occupants swapped: Tech Stack Freshness → Learning Systems Design impact · Business Impact → Pedagogy Initiative Impact. The refresh audit still runs — 100% of the surface audited each cycle, rebuilt where the audit calls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Cost bars scale with domain complexity, and every number here is adjustable as real costs land: an objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · a coding question under ₹100 baseline — ~₹200 where a question is effectively a project (FullStack, GenAI), up to ₹300 where it ships editorials, brute-force and efficient solutions (DS &amp; Algo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>CWT — complexity-weighted topics: topic count × the domain complexity multiplier. ≈ 200 CWT per AI Engineer per 6-month cycle (= ≈ 100 topics at FullStack / GenAI 2.0×); a Senior holds ≈ 400.</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1077,7 @@
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1046,7 +1109,7 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1078,7 +1141,7 @@
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1110,7 +1173,7 @@
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1142,7 +1205,7 @@
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1174,7 +1237,7 @@
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1206,7 +1269,7 @@
       </c>
     </row>
     <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1238,7 +1301,7 @@
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1270,7 +1333,7 @@
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1302,7 +1365,7 @@
       </c>
     </row>
     <row r="12" ht="104" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1334,7 +1397,7 @@
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1366,7 +1429,7 @@
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1398,7 +1461,7 @@
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1430,7 +1493,7 @@
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1462,7 +1525,7 @@
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1494,7 +1557,7 @@
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1526,7 +1589,7 @@
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1558,7 +1621,7 @@
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1590,7 +1653,7 @@
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1622,7 +1685,7 @@
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1654,7 +1717,7 @@
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1742,7 +1805,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1752,7 +1815,7 @@
           <t>Scope of Work</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -1764,7 +1827,7 @@
       </c>
     </row>
     <row r="4" ht="39" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1774,7 +1837,7 @@
           <t>Influence</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -1786,7 +1849,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1796,7 +1859,7 @@
           <t>Content Quality</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate · Module-Quiz Score Bands</t>
         </is>
@@ -1808,7 +1871,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1818,7 +1881,7 @@
           <t>Content Effectiveness</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Learner Accessed Content Completion Rate · Practice Attempt-to-Completion Rate · Engagement-Matrix Cell Migration · Summative + Formative Achievement</t>
         </is>
@@ -1830,7 +1893,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1840,7 +1903,7 @@
           <t>Curriculum Design</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Pedagogy Initiative Impact · University Curriculum Compliance</t>
         </is>
@@ -1852,7 +1915,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1862,7 +1925,7 @@
           <t>Content Velocity</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Learning Content Hours Delivered · Vernacular Content Hours Delivered · Practice &amp; Assessment Content Pieces Delivered</t>
         </is>
@@ -1874,7 +1937,7 @@
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1884,7 +1947,7 @@
           <t>Industry Upgrades</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Industry Update Adherence · Tech Stack Freshness Rate</t>
         </is>
@@ -1896,7 +1959,7 @@
       </c>
     </row>
     <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1906,7 +1969,7 @@
           <t>Production Systems</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Agentic Production Coverage</t>
         </is>
@@ -1918,7 +1981,7 @@
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1928,7 +1991,7 @@
           <t>Learning Systems Design</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Evaluation Environment Coverage · Domain Capability Delivery · Summative + Formative Achievement · Module-Quiz Score Bands</t>
         </is>
@@ -1940,7 +2003,7 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1950,7 +2013,7 @@
           <t>GenAI Orchestration &amp; Content Automation</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Agentic Production Coverage · Cost per MCQ Generated · Cost per Coding Question</t>
         </is>
@@ -1962,7 +2025,7 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1972,7 +2035,7 @@
           <t>Business Impact</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Summative Skill Assessment Achievement Rate · Formative Skill Assessment Achievement Rate · Graded Assessment Achievement Rate (NIAT) · Weekly Active Users (Launchpad)</t>
         </is>
@@ -1984,7 +2047,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1994,7 +2057,7 @@
           <t>Problem Solving</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2006,7 +2069,7 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2016,7 +2079,7 @@
           <t>Execution</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate · Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -2028,7 +2091,7 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2038,7 +2101,7 @@
           <t>Learnability</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2050,7 +2113,7 @@
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2060,7 +2123,7 @@
           <t>Communication</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2072,7 +2135,7 @@
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2082,7 +2145,7 @@
           <t>Ambiguity Handling</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2094,7 +2157,7 @@
       </c>
     </row>
     <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2104,7 +2167,7 @@
           <t>Best Practices</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Cost of Operations · Creative Resource Utilisation Rate</t>
         </is>
@@ -2116,7 +2179,7 @@
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2126,7 +2189,7 @@
           <t>Cross-Functionality</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate</t>
         </is>
@@ -2138,7 +2201,7 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2148,7 +2211,7 @@
           <t>Stakeholder Collaboration</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -2160,7 +2223,7 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2170,7 +2233,7 @@
           <t>Cross-Product Work</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2182,7 +2245,7 @@
       </c>
     </row>
     <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2192,7 +2255,7 @@
           <t>Mentorship</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Power Performers Created</t>
         </is>
@@ -2275,7 +2338,7 @@
           <t>Assessment score improvements, competency progression</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Summative + Formative Skill Assessment Achievement · org KRA 1 SPI Score Bands</t>
         </is>
@@ -2297,7 +2360,7 @@
           <t>Issues resolved within SLA, quality of implementation</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate</t>
         </is>
@@ -2319,7 +2382,7 @@
           <t>Planned updates on schedule, emerging skills coverage</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Industry Update Adherence · Tech Stack Freshness Rate</t>
         </is>
@@ -2341,7 +2404,7 @@
           <t>Concept understanding improvements, completion rates, delivery innovation</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Pedagogy Initiative Impact · Agentic Production Coverage</t>
         </is>
@@ -2385,7 +2448,7 @@
           <t>Pedagogical excellence, content coherence, engagement quality</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Content Issue Recurrence Rate · Module-Quiz Score Bands · Engagement-Matrix Cell Migration</t>
         </is>
@@ -2407,7 +2470,7 @@
           <t>Effective use of AI for content production, quality of automation systems, cost/velocity optimization through AI, team GenAI capability development</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Agentic Production Coverage</t>
         </is>
@@ -2429,7 +2492,7 @@
           <t>Cost per learning hour, cost per assessment, resource optimization</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Cost per Learning Hour · Cost per MCQ · Cost per Coding Question</t>
         </is>
@@ -2451,7 +2514,7 @@
           <t>Monthly content hours delivery, practice/assessment production</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Learning Content Hours Delivered · Practice &amp; Assessment Content Pieces Delivered</t>
         </is>
@@ -2473,7 +2536,7 @@
           <t>Request fulfillment within timeframes, stakeholder satisfaction</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate · Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -2517,7 +2580,7 @@
           <t>Members ready for next level, training program design</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Power Performers Created</t>
         </is>
@@ -2539,7 +2602,7 @@
           <t>Regular 1-on-1s, actionable feedback, development plan clarity</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2561,7 +2624,7 @@
           <t>Active participation, candidate evaluation quality, new hire success rate</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Hires Made · Cost per Hire</t>
         </is>
@@ -2583,7 +2646,7 @@
           <t>High potential recognition, development opportunities, succession planning</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Team Retention Rate</t>
         </is>
@@ -2605,7 +2668,7 @@
           <t>Stretch assignments, cross-functional exposure, leadership development</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2649,7 +2712,7 @@
           <t>Following org processes, execution consistency</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2671,7 +2734,7 @@
           <t>Conducting learning hours, knowledge sharing, skill development</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2693,7 +2756,7 @@
           <t>Business impact focus vs. volume, quality over quantity</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2715,7 +2778,7 @@
           <t>Staying current with trends, learning from new tech, embracing change</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2737,7 +2800,7 @@
           <t>Living company values, brand protection, mission-driven decisions</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -9,11 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ladder" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates &amp; Scope" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Areas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Wiring" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rating Framework" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Manager" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stay Bars" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Areas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Wiring" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rating Framework" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Manager" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +63,24 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B4F43"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="008A2C18"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
@@ -89,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -111,11 +130,55 @@
         <color rgb="FFCCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -136,10 +199,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -706,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -890,7 +964,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
+    <row r="18" ht="56" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>One rule</t>
@@ -898,111 +972,19 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>The gates say how you climb; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Associate AI Engineer (internship)</t>
+          <t>The gates say how you climb; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Per-rung matrices</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>The readiness scorecard filling on schedule: A1 shown (assigned pipelines run unsupervised), then A2 (a documented before/after on an agent's accuracy, retrieval quality or unit cost) — never more than one month behind the ramp plan across the six.
-Governance from day one: issue recurrence ≤ 2% on their items · unit costs inside the cost bars on their pipelines (≤ ₹3 an objective practice item; coding questions on the domain scale below) · worklogs complete, statuses current.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="146" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>The four output rows at budget each cycle: Tech Stack Freshness Rate 100% on their ≈ 200 CWT surface (≈ 100 topics at FullStack / GenAI complexity, double on lighter domains) · their CWT share of the team's Learning Content Hours + Practice &amp; Assessment Pieces · Agentic Production Coverage 90% · Summative 35% + Formative 23% on their modules.
-2–3 content agents built and adopted (A3) by year-end — mandatory for the rung, not just scored.
-The four governance rows never breached: issue resolution 80% inside the 2-day TAT · recurrence ≤ 2% · unit costs at budget (≤ ₹10,000 a learning hour · ≤ ₹3 an objective practice item — FIB, MCQ, MMCQ, any type · coding questions under ₹100, scaled by domain below) · sprint delivery 100% + stakeholder fulfillment 90%. A breach zeroes that slice and blocks eligibility for the cycle.
-Rating floor: Performance + Role Competence pillars in band.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>The ≈ 400 CWT surface (2× an AI Engineer, complexity-weighted) held at budget — Senior isn't a medal, it's a load; the slice doesn't quietly shrink.
-A4 live: production coverage attributable to multi-agent systems they own · all their Section B rows at budget 2+ consecutive cycles · unit costs at or below budget, and falling.
-Mentorship on record: ≥ 1 power performer contributed in the trailing 12 months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>AI Engineer Lead</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>The team's owned rows at budget at review — ≥ 85% of them (FS pilot: 29 rows) ⚑ — with team Freshness at 100% and team production coverage at 90%, run through people, not personally.
-Business impact at budget on the team's domains: Summative 35% · Formative 23% · SPI band contribution.
-People outcomes as governance: Team Retention ≥ 90% trailing 12 months · ≥ 1 Power Performer created per appraisal cycle · Cost of Operations at plan + Roadmap ≥ 90% (run by the team's PM, answered for by the Lead) · stakeholder 90% + sprint 100%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>AI Engineer 3</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Reads through department KPIs and org KRAs, not one team view — the bar stays directional until those budgets land: the standards they authored still adopted and alive · portfolio Section B healthy across teams · a Lead bench ready behind them · places the org's learning-systems bets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Low-refresh domains (English, Aptitude, Mathematics, Programming, CS Core, DS &amp; Algo, DevOps, System Design) run the same bar with two occupants swapped: Tech Stack Freshness → Learning Systems Design impact · Business Impact → Pedagogy Initiative Impact. The refresh audit still runs — 100% of the surface audited each cycle, rebuilt where the audit calls.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="56" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Cost bars scale with domain complexity, and every number here is adjustable as real costs land: an objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · a coding question under ₹100 baseline — ~₹200 where a question is effectively a project (FullStack, GenAI), up to ₹300 where it ships editorials, brute-force and efficient solutions (DS &amp; Algo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>CWT — complexity-weighted topics: topic count × the domain complexity multiplier. ≈ 200 CWT per AI Engineer per 6-month cycle (= ≈ 100 topics at FullStack / GenAI 2.0×); a Senior holds ≈ 400.</t>
+          <t>See the Stay Bars tab — each rung's eight rows in the merit-matrix format (Category · Row · Bar · Gate · Weight), with the domain-scaled numbers spelled out.</t>
         </is>
       </c>
     </row>
@@ -1015,6 +997,1178 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0E6E5C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Holding the role — each rung's stay bar as its eight scored rows (4 output + 4 governance × 12.5%). The gates say how you climb; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>How to read the gate column: Mandatory = the rung's defining requirement · Breach blocks = a breach zeroes that 12.5% slice and blocks eligibility for the cycle · ⚑ = a number not locked yet (a proposed default, adjustable).  Domain chips — build complexity sets the topic count behind the same ≈ 200 CWT per cycle: Low 1.0× — English · Aptitude · Mathematics Medium 1.5× — Programming · CS Core · DevOps High 2.0× — FullStack · GenAI Very High 2.5× — System Design · DS &amp; Algo · DS / ML · low-churn marks the two slots that swap on low-refresh domains (note below).</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="9" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Associate AI Engineer (internship)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>A readiness scorecard — read ready / not ready. Interns answer for no team rows by design.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Bar — hold at 100%</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Agent Pipeline Operation (A1)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Assigned pipelines run unsupervised — two consecutive months</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Agent Improvement Delta (A2)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>≥ 1 documented before/after on an agent's accuracy, retrieval quality or unit cost</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Domain floor output</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>⚑ propose: 25% of an AI Engineer's monthly share, produced hands-on (FS: ≈ 12 hrs · 400 pieces)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Review judgment</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>The responsible reviewer signs off their review calls on real work</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Content Issue Recurrence — their items</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>≤ 2%</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="43" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Unit costs — their pipelines</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · coding question on the domain scale ~₹200 FullStack / GenAI up to ₹300 DS &amp; Algo</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Worklog &amp; Status Hygiene</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>100% — worklogs complete, statuses current</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Culture &amp; Values pillar</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>In band</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Ramp cadence: A1 shown, then A2 — never more than one month behind the ramp plan across the six.</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="9" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Bar — hold at 100%</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Tech Stack Freshness Rate low-churn: slot → Learning Systems Design impact</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>100% of the ≈ 200 CWT surface each 6-month cycle — 200 topics 133 topics 100 topics 80 topics</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Below 90% blocks ⚑</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Learning Content Hours + Practice &amp; Assessment Pieces</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Their CWT share of the team budget (FS team: 50 hrs · 1,600 pieces a month)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>At budget</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Agentic Production Coverage</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>90% — with 2–3 content agents built and adopted (A3) by year-end</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Agents mandatory</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Summative + Formative Achievement low-churn: slot → Pedagogy Initiative Impact</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Summative 35% quarterly · Formative 23% monthly, on their modules</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>At budget</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Content Issue Resolution Efficiency</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>80% inside the 2-day TAT</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Content Issue Recurrence</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>≤ 2%</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="43" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Unit costs</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>CpLH ≤ ₹10,000 · objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · coding question under ₹100 baseline ~₹200 FullStack / GenAI up to ₹300 DS &amp; Algo</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Sprint Delivery + Stakeholder Fulfillment</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 100% · stakeholder 90%</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Rating floor: Performance + Role Competence pillars in band.</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="9" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Bar — hold at 100%</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="43" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Complexity-weighted surface</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>≈ 400 CWT held at budget — 2× an AI Engineer; Senior isn't a medal, it's a load, and the slice doesn't quietly shrink</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Learning Systems Design impact</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>⚑ review evidence until budgets land (engagement-experience contribution + drop-off/completion delta)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Review-based</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Agent Orchestration (A4)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>90% production coverage attributable to multi-agent systems they own</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Pedagogy Initiative Impact</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>⚑ review evidence until a budget lands</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Review-based</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Their Section B rows</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>All at budget, 2+ consecutive cycles</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Content Issue Recurrence — wider slice</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>≤ 2%</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Unit-cost trend — their courses</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>At or below budget, and falling</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Mentorship on record</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>≥ 1 power performer contributed, trailing 12 months (adjustable)</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>AI Engineer Lead</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Bar — hold at 100%</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Team Section B in-band rate</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>⚑ propose: ≥ 85% of the team's owned rows at budget (FS pilot: 29 rows)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Team Tech Stack Freshness</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>100% across the team's whole surface</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Below 90% blocks ⚑</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Team Agentic Production Coverage</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>90% — run through people, not personally</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Business impact — the team's domains</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Summative 35% · Formative 23% · SPI band contribution</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>At budget</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Team Retention Rate</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>≥ 90%, trailing 12 months (adjustable)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Power Performers Created</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>≥ 1 per appraisal cycle (adjustable)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Cost of Operations + Roadmap</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>At plan ⚑ · ≥ 90% ⚑ — run by the team's PM, answered for by the Lead</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Stakeholder Fulfillment + Sprint Delivery</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Stakeholder 90% · sprint 100%</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>AI Engineer 3</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Reads through department KPIs and org KRAs, not one team view — the bar stays directional until those budgets land: the standards they authored still adopted and alive · portfolio Section B healthy across teams · a Lead bench ready behind them · places the org's learning-systems bets.</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="9" t="n"/>
+    </row>
+    <row r="52" ht="56" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Low-refresh domains (English, Aptitude, Mathematics, Programming, CS Core, DS &amp; Algo, DevOps, System Design) run the same bar with two occupants swapped: Tech Stack Freshness → Learning Systems Design impact · Business Impact → Pedagogy Initiative Impact. The refresh audit still runs — 100% of the surface audited each cycle, rebuilt where the audit calls.</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="9" t="n"/>
+    </row>
+    <row r="53" ht="56" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Cost bars scale with domain complexity, and every number here is adjustable as real costs land: an objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · a coding question under ₹100 baseline — ~₹200 where a question is effectively a project (FullStack, GenAI), up to ₹300 where it ships editorials, brute-force and efficient solutions (DS &amp; Algo).</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="9" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>CWT — complexity-weighted topics: topic count × the domain complexity multiplier. ≈ 200 CWT per AI Engineer per 6-month cycle (= ≈ 100 topics at FullStack / GenAI 2.0×); a Senior holds ≈ 400.</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B14:E14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
@@ -1077,7 +2231,7 @@
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1109,7 +2263,7 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1141,7 +2295,7 @@
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1173,7 +2327,7 @@
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1205,7 +2359,7 @@
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1237,7 +2391,7 @@
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1269,7 +2423,7 @@
       </c>
     </row>
     <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1301,7 +2455,7 @@
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1333,7 +2487,7 @@
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1365,7 +2519,7 @@
       </c>
     </row>
     <row r="12" ht="104" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1397,7 +2551,7 @@
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1429,7 +2583,7 @@
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1461,7 +2615,7 @@
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1493,7 +2647,7 @@
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1525,7 +2679,7 @@
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1557,7 +2711,7 @@
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1589,7 +2743,7 @@
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -1621,7 +2775,7 @@
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1653,7 +2807,7 @@
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1685,7 +2839,7 @@
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1717,7 +2871,7 @@
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -1756,7 +2910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
@@ -1805,7 +2959,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1815,7 +2969,7 @@
           <t>Scope of Work</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -1827,7 +2981,7 @@
       </c>
     </row>
     <row r="4" ht="39" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Foundation</t>
         </is>
@@ -1837,7 +2991,7 @@
           <t>Influence</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -1849,7 +3003,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1859,7 +3013,7 @@
           <t>Content Quality</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate · Module-Quiz Score Bands</t>
         </is>
@@ -1871,7 +3025,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1881,7 +3035,7 @@
           <t>Content Effectiveness</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Learner Accessed Content Completion Rate · Practice Attempt-to-Completion Rate · Engagement-Matrix Cell Migration · Summative + Formative Achievement</t>
         </is>
@@ -1893,7 +3047,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1903,7 +3057,7 @@
           <t>Curriculum Design</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Pedagogy Initiative Impact · University Curriculum Compliance</t>
         </is>
@@ -1915,7 +3069,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1925,7 +3079,7 @@
           <t>Content Velocity</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Learning Content Hours Delivered · Vernacular Content Hours Delivered · Practice &amp; Assessment Content Pieces Delivered</t>
         </is>
@@ -1937,7 +3091,7 @@
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1947,7 +3101,7 @@
           <t>Industry Upgrades</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Industry Update Adherence · Tech Stack Freshness Rate</t>
         </is>
@@ -1959,7 +3113,7 @@
       </c>
     </row>
     <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1969,7 +3123,7 @@
           <t>Production Systems</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Agentic Production Coverage</t>
         </is>
@@ -1981,7 +3135,7 @@
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -1991,7 +3145,7 @@
           <t>Learning Systems Design</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Evaluation Environment Coverage · Domain Capability Delivery · Summative + Formative Achievement · Module-Quiz Score Bands</t>
         </is>
@@ -2003,7 +3157,7 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -2013,7 +3167,7 @@
           <t>GenAI Orchestration &amp; Content Automation</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Agentic Production Coverage · Cost per MCQ Generated · Cost per Coding Question</t>
         </is>
@@ -2025,7 +3179,7 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Core Creation and Quality</t>
         </is>
@@ -2035,7 +3189,7 @@
           <t>Business Impact</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Summative Skill Assessment Achievement Rate · Formative Skill Assessment Achievement Rate · Graded Assessment Achievement Rate (NIAT) · Weekly Active Users (Launchpad)</t>
         </is>
@@ -2047,7 +3201,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2057,7 +3211,7 @@
           <t>Problem Solving</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2069,7 +3223,7 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2079,7 +3233,7 @@
           <t>Execution</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate · Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -2091,7 +3245,7 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2101,7 +3255,7 @@
           <t>Learnability</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2113,7 +3267,7 @@
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2123,7 +3277,7 @@
           <t>Communication</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2135,7 +3289,7 @@
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2145,7 +3299,7 @@
           <t>Ambiguity Handling</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2157,7 +3311,7 @@
       </c>
     </row>
     <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
@@ -2167,7 +3321,7 @@
           <t>Best Practices</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Cost of Operations · Creative Resource Utilisation Rate</t>
         </is>
@@ -2179,7 +3333,7 @@
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2189,7 +3343,7 @@
           <t>Cross-Functionality</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate</t>
         </is>
@@ -2201,7 +3355,7 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2211,7 +3365,7 @@
           <t>Stakeholder Collaboration</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -2223,7 +3377,7 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2233,7 +3387,7 @@
           <t>Cross-Product Work</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>— (by design)</t>
         </is>
@@ -2245,7 +3399,7 @@
       </c>
     </row>
     <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Collaboration and Stakeholders</t>
         </is>
@@ -2255,7 +3409,7 @@
           <t>Mentorship</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Power Performers Created</t>
         </is>
@@ -2274,7 +3428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
@@ -2338,7 +3492,7 @@
           <t>Assessment score improvements, competency progression</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Summative + Formative Skill Assessment Achievement · org KRA 1 SPI Score Bands</t>
         </is>
@@ -2360,7 +3514,7 @@
           <t>Issues resolved within SLA, quality of implementation</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate</t>
         </is>
@@ -2382,7 +3536,7 @@
           <t>Planned updates on schedule, emerging skills coverage</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Industry Update Adherence · Tech Stack Freshness Rate</t>
         </is>
@@ -2404,7 +3558,7 @@
           <t>Concept understanding improvements, completion rates, delivery innovation</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Pedagogy Initiative Impact · Agentic Production Coverage</t>
         </is>
@@ -2448,7 +3602,7 @@
           <t>Pedagogical excellence, content coherence, engagement quality</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Content Issue Recurrence Rate · Module-Quiz Score Bands · Engagement-Matrix Cell Migration</t>
         </is>
@@ -2470,7 +3624,7 @@
           <t>Effective use of AI for content production, quality of automation systems, cost/velocity optimization through AI, team GenAI capability development</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Agentic Production Coverage</t>
         </is>
@@ -2492,7 +3646,7 @@
           <t>Cost per learning hour, cost per assessment, resource optimization</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Cost per Learning Hour · Cost per MCQ · Cost per Coding Question</t>
         </is>
@@ -2514,7 +3668,7 @@
           <t>Monthly content hours delivery, practice/assessment production</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Learning Content Hours Delivered · Practice &amp; Assessment Content Pieces Delivered</t>
         </is>
@@ -2536,7 +3690,7 @@
           <t>Request fulfillment within timeframes, stakeholder satisfaction</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Cross-functional Sprint Delivery Rate · Stakeholder Content Request Fulfillment Rate</t>
         </is>
@@ -2580,7 +3734,7 @@
           <t>Members ready for next level, training program design</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Power Performers Created</t>
         </is>
@@ -2602,7 +3756,7 @@
           <t>Regular 1-on-1s, actionable feedback, development plan clarity</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2624,7 +3778,7 @@
           <t>Active participation, candidate evaluation quality, new hire success rate</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Hires Made · Cost per Hire</t>
         </is>
@@ -2646,7 +3800,7 @@
           <t>High potential recognition, development opportunities, succession planning</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Team Retention Rate</t>
         </is>
@@ -2668,7 +3822,7 @@
           <t>Stretch assignments, cross-functional exposure, leadership development</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2712,7 +3866,7 @@
           <t>Following org processes, execution consistency</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2734,7 +3888,7 @@
           <t>Conducting learning hours, knowledge sharing, skill development</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2756,7 +3910,7 @@
           <t>Business impact focus vs. volume, quality over quantity</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2778,7 +3932,7 @@
           <t>Staying current with trends, learning from new tech, embracing change</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2800,7 +3954,7 @@
           <t>Living company values, brand protection, mission-driven decisions</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Review-based — no KPI row by design</t>
         </is>
@@ -2935,7 +4089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>
@@ -3717,7 +4871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0E6E5C"/>

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate · Module-Quiz Score Bands</t>
+          <t>Content Issue Resolution Efficiency · Content Issue Recurrence Rate · Practice → Module-Quiz Conversion</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Evaluation Environment Coverage · Domain Capability Delivery · Summative + Formative Achievement · Module-Quiz Score Bands</t>
+          <t>Evaluation Environment Coverage · Domain Capability Delivery · Summative + Formative Achievement · Module-Quiz → Formative Conversion</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>The Domain Product Enablement pair — raised/accepted by SMEs, built by PMs + Engineering, accountability in Learning Domains — plus the measurement proof: achievement and quiz-band reads shared with Content Effectiveness / Content Quality (the APC double-read precedent). Also reads: Learning Environment Satisfaction, PAtC env-friction leg.</t>
+          <t>The Domain Product Enablement pair — raised/accepted by SMEs, built by PMs + Engineering, accountability in Learning Domains — plus the measurement proof: achievement and conversion-chain reads shared with Content Effectiveness / Content Quality (the APC double-read precedent). Also reads: Learning Environment Satisfaction, PAtC env-friction leg.</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Agentic Production Coverage · Cost per MCQ Generated · Cost per Coding Question</t>
+          <t>Agentic Production Coverage · Cost per Objective Practice Item · Cost per Coding Question</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Content Issue Recurrence Rate · Module-Quiz Score Bands · Engagement-Matrix Cell Migration</t>
+          <t>Content Issue Recurrence Rate · Practice → Module-Quiz Conversion · Engagement-Matrix Cell Migration</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Cost per Learning Hour · Cost per MCQ · Cost per Coding Question</t>
+          <t>Cost per Learning Hour · Cost per Objective Practice Item · Cost per Coding Question</t>
         </is>
       </c>
     </row>

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -901,7 +901,7 @@
         <is>
           <t>1. Runs assigned agent pipelines end-to-end without supervision — prompts tuned, outputs reviewed, escalations handled (A1–A2 shown).
 2. Judgment demonstrated: the responsible reviewer — their mentoring AI Engineer or Senior — confirms the intern's reviews catch what their own review would catch, sampled on real work through the ramp; they can tell good output from plausible output.
-3. Domain floor: has produced representative content items manually during the ramp — you can't review what you can't do.
+3. Domain floor: has produced representative content items manually during the ramp — ⚑ propose: ≈ 25% of an AI Engineer's monthly share, held as ramp evidence — you can't review what you can't do.
 4. Decided by: supervising Senior / AI Engineer Lead proposes with ramp evidence; HOD confirms. Package set by HR at conversion.</t>
         </is>
       </c>
@@ -1003,7 +1003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>How to read the gate column: Mandatory = the rung's defining requirement · Breach blocks = a breach zeroes that 12.5% slice and blocks eligibility for the cycle · ⚑ = a number not locked yet (a proposed default, adjustable).  Domain chips — build complexity sets the topic count behind the same ≈ 200 CWT per cycle: Low 1.0× — English · Aptitude · Mathematics Medium 1.5× — Programming · CS Core · DevOps High 2.0× — FullStack · GenAI Very High 2.5× — System Design · DS &amp; Algo · DS / ML · low-churn marks the two slots that swap on low-refresh domains (note below).</t>
+          <t>How to read the gate column: Mandatory = the rung's defining requirement · Breach blocks = a breach zeroes that 12.5% slice and blocks eligibility for the cycle · ⚑ = a number not locked yet (a proposed default, adjustable). One gate above every table: a Culture &amp; Values flag in the cycle blocks eligibility whatever the score — culture is rated in the pillars (10%), never scored as a row.  Domain chips — build complexity sets the topic count behind the same ≈ 200 CWT per cycle: Low 1.0× — English · Aptitude · Mathematics Medium 1.5× — Programming · CS Core · DevOps High 2.0× — FullStack · GenAI Very High 2.5× — System Design · DS &amp; Algo · DS / ML.</t>
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="43" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Agent Pipeline Operation (A1)</t>
+          <t>Content quality &amp; standards</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Assigned pipelines run unsupervised — two consecutive months</t>
+          <t>Work ships simplified, aesthetic, technically accurate, to the team's standards — accepted first-pass through review</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="43" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Agent Improvement Delta (A2)</t>
+          <t>Agent improvement delta (A2)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>≥ 1 documented before/after on an agent's accuracy, retrieval quality or unit cost</t>
+          <t>⚑ ≥ 4 documented before/afters on accuracy, retrieval quality or unit cost — spread across the agents they run, not four tweaks to one</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Domain floor output</t>
+          <t>Their topic surface</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>⚑ propose: 25% of an AI Engineer's monthly share, produced hands-on (FS: ≈ 12 hrs · 400 pieces)</t>
+          <t>⚑ Half an AI Engineer's — ≈ 100 CWT across the six months, produced through the agents</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="56" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Review judgment</t>
+          <t>Feedback → backpropagation plans</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>The responsible reviewer signs off their review calls on real work</t>
+          <t>Runs the feedback agents — reactive and proactive channels, every dimension — and outputs the plan; review inputs logged by the mentoring AI Engineer reach zero by the final two months</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Content Issue Recurrence — their items</t>
+          <t>Content issues — their items</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>≤ 2%</t>
+          <t>80% fixed inside the 2-day TAT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="43" customHeight="1">
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1224,66 +1224,66 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>Recurrence — their items</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>≤ 2% — fixes stay fixed</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Process adherence</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>The team's guidelines followed end-to-end — checklists, review sheets, worklogs current</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="43" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>Unit costs — their pipelines</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · coding question on the domain scale ~₹200 FullStack / GenAI up to ₹300 DS &amp; Algo</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Worklog &amp; Status Hygiene</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>100% — worklogs complete, statuses current</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Culture &amp; Values pillar</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>In band</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1305,97 +1305,85 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ramp cadence: A1 shown, then A2 — never more than one month behind the ramp plan across the six.</t>
+          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead (≥ 85% of rows in band) and run day to day by the PM.</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="n"/>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Ramp cadence: A1 shown, then A2 — never more than one month behind the ramp plan across the six. The hands-on domain floor (items produced manually) is conversion-gate evidence, not a monthly row.</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="9" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>AI Engineer</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="9" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Bar — hold at 100%</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="19" ht="43" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Tech Stack Freshness Rate low-churn: slot → Learning Systems Design impact</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>100% of the ≈ 200 CWT surface each 6-month cycle — 200 topics 133 topics 100 topics 80 topics</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Tech Stack Freshness Rate</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>100% of their domain's surface — ≈ 200 CWT each 6-month cycle; the domain = its set of courses, across all products — 200 topics 133 topics 100 topics 80 topics</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Below 90% blocks ⚑</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>A — Output</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Learning Content Hours + Practice &amp; Assessment Pieces</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Their CWT share of the team budget (FS team: 50 hrs · 1,600 pieces a month)</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>At budget</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1431,7 +1419,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="43" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1439,17 +1427,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Summative + Formative Achievement low-churn: slot → Pedagogy Initiative Impact</t>
+          <t>Pedagogy Initiative Impact</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Summative 35% quarterly · Formative 23% monthly, on their modules</t>
+          <t>Their domain's students land the org SPI bands — 30% at ≥ 8.0 · 40% at 7.0–8.0 · 30% at 6.0–7.0 (two-sided with Assessments, same as the conversion chain)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>At budget</t>
+          <t>At the bands ⚑</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1458,25 +1446,25 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
+    <row r="22" ht="43" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Content Issue Resolution Efficiency</t>
+          <t>Learning Systems Design impact</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>80% inside the 2-day TAT</t>
+          <t>The domain's learner-facing capabilities built and adopted — evaluation environments included — with Learning Environment Satisfaction holding 4.5 / 5 on them</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>At budget ⚑</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1493,567 +1481,543 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>Content Issue Resolution Efficiency</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>80% inside the 2-day TAT</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>Content Issue Recurrence</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>≤ 2%</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Breach blocks</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="43" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+    <row r="25" ht="43" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Unit costs</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>CpLH ≤ ₹10,000 · objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · coding question under ₹100 baseline ~₹200 FullStack / GenAI up to ₹300 DS &amp; Algo</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Breach blocks</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Sprint Delivery + Stakeholder Fulfillment</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Sprint 100% · stakeholder 90%</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Breach blocks</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead (≥ 85% of rows in band) and run day to day by the PM.</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Rating floor: Performance + Role Competence pillars in band.</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="9" t="n"/>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="9" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Bar — hold at 100%</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="43" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="32" ht="43" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Complexity-weighted surface</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>≈ 400 CWT held at budget — 2× an AI Engineer; Senior isn't a medal, it's a load, and the slice doesn't quietly shrink</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Tech Stack Freshness Rate</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Double an AI Engineer — ≈ 400 CWT per cycle, across domains, all products; Senior isn't a medal, it's a load, and the slice doesn't quietly shrink</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Below 90% blocks ⚑</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Content agents across domains (A4)</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>The agents they build or pick run in every domain's production — 90% coverage attributable to them</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Learning Systems Design impact</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>⚑ review evidence until budgets land (engagement-experience contribution + drop-off/completion delta)</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Review-based</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>⚑ 6–10 learner-facing initiatives a year, proposed and implemented — Adaptive Objective Practice, Adaptive Coding Practice, Programming Coach and the like — moving the conversion chain for all products</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Agent Orchestration (A4)</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>90% production coverage attributable to multi-agent systems they own</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Pedagogy Initiative Impact</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Those initiatives pedagogically grounded — baseline agreed before launch — and the SPI bands hold across every domain they touch; the surface, not the activity, separates this from an AI Engineer</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>At the bands ⚑</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Content issues — wider slice</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>80% inside the 2-day TAT · recurrence ≤ 2%, across the courses they answer for</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="43" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Topic production cost — their courses</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Every unit cost at or below budget (CpLH ₹10,000 · item ₹3 · coding ₹100–₹300) and falling year on year — ⚑ −40% the target, −10% the minimum direction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Sprint Delivery + Stakeholder Fulfillment</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 100% · stakeholder 90% — they raise the Section C asks</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Mentorship on record</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>≥ 1 power performer contributed, trailing 12 months (adjustable)</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead (≥ 85% of rows in band) and run day to day by the PM.</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="9" t="n"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>AI Engineer Lead</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Bar — hold at 100%</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Team Section B in-band rate</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>⚑ propose: ≥ 85% of the team's owned rows at budget (FS pilot: 29 rows)</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Pedagogy Initiative Impact</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>⚑ review evidence until a budget lands</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Review-based</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Team Tech Stack Freshness</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>100% across the team's whole surface</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Below 90% blocks ⚑</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Their Section B rows</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>All at budget, 2+ consecutive cycles</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Team Agentic Production Coverage</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>90% — run through people, not personally</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Content Issue Recurrence — wider slice</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>≤ 2%</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Unit-cost trend — their courses</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>At or below budget, and falling</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Mentorship on record</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>≥ 1 power performer contributed, trailing 12 months (adjustable)</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>AI Engineer Lead</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Row</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Bar — hold at 100%</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Team Section B in-band rate</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>⚑ propose: ≥ 85% of the team's owned rows at budget (FS pilot: 29 rows)</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>A — Output</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Team Tech Stack Freshness</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>100% across the team's whole surface</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Below 90% blocks ⚑</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>A — Output</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Team Agentic Production Coverage</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>90% — run through people, not personally</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>A — Output</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Business impact — the team's domains</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Summative 35% · Formative 23% · SPI band contribution</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>At budget</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Team Retention Rate</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>≥ 90%, trailing 12 months (adjustable)</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Power Performers Created</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>≥ 1 per appraisal cycle (adjustable)</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Cost of Operations + Roadmap</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>At plan ⚑ · ≥ 90% ⚑ — run by the team's PM, answered for by the Lead</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2070,41 +2034,107 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
+          <t>Team Retention Rate</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>≥ 90%, trailing 12 months (adjustable)</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Power Performers Created</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>≥ 1 per appraisal cycle (adjustable)</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Cost of Operations + Roadmap</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>At plan ⚑ · ≥ 90% ⚑ — run by the team's PM, answered for by the Lead</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>Stakeholder Fulfillment + Sprint Delivery</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Stakeholder 90% · sprint 100%</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Breach blocks</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>AI Engineer 3</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Reads through department KPIs and org KRAs, not one team view — the bar stays directional until those budgets land: the standards they authored still adopted and alive · portfolio Section B healthy across teams · a Lead bench ready behind them · places the org's learning-systems bets.</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="9" t="n"/>
-    </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="16" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Note</t>
@@ -2112,53 +2142,87 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Low-refresh domains (English, Aptitude, Mathematics, Programming, CS Core, DS &amp; Algo, DevOps, System Design) run the same bar with two occupants swapped: Tech Stack Freshness → Learning Systems Design impact · Business Impact → Pedagogy Initiative Impact. The refresh audit still runs — 100% of the surface audited each cycle, rebuilt where the audit calls.</t>
+          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead (≥ 85% of rows in band) and run day to day by the PM.</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="9" t="n"/>
     </row>
-    <row r="53" ht="56" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Cost bars scale with domain complexity, and every number here is adjustable as real costs land: an objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · a coding question under ₹100 baseline — ~₹200 where a question is effectively a project (FullStack, GenAI), up to ₹300 where it ships editorials, brute-force and efficient solutions (DS &amp; Algo).</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="9" t="n"/>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>AI Engineer 3</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>CWT — complexity-weighted topics: topic count × the domain complexity multiplier. ≈ 200 CWT per AI Engineer per 6-month cycle (= ≈ 100 topics at FullStack / GenAI 2.0×); a Senior holds ≈ 400.</t>
+          <t>Reads through department KPIs and org KRAs, not one team view — the bar stays directional until those budgets land: the standards they authored still adopted and alive · portfolio Section B healthy across teams · a Lead bench ready behind them · places the org's learning-systems bets.</t>
         </is>
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="9" t="n"/>
     </row>
+    <row r="56" ht="56" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Low-refresh domains (English, Aptitude, Mathematics, Programming, CS Core, DS &amp; Algo, DevOps, System Design) run the same eight rows — no slot swaps: Pedagogy Initiative Impact and Learning Systems Design impact are standard occupants for everyone now. The freshness bar is 100% of whatever the audit calls, so a low-churn domain simply has a smaller refresh surface; the freed capacity goes to the LSD and PII rows.</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="9" t="n"/>
+    </row>
+    <row r="57" ht="56" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Cost bars scale with domain complexity, and every number here is adjustable as real costs land: an objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · a coding question under ₹100 baseline — ~₹200 where a question is effectively a project (FullStack, GenAI), up to ₹300 where it ships editorials, brute-force and efficient solutions (DS &amp; Algo).</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="9" t="n"/>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>CWT — complexity-weighted topics: topic count × the domain complexity multiplier. ≈ 200 CWT per AI Engineer per 6-month cycle (= ≈ 100 topics at FullStack / GenAI 2.0×); a Senior holds ≈ 400.</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B26:E26"/>
+  <mergeCells count="16">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B57:E57"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B30:E30"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B16:E16"/>
     <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B28:E28"/>
@@ -2230,7 +2294,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
+    <row r="3" ht="52" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Foundation</t>
@@ -2238,27 +2302,27 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Scope of Work</t>
+          <t>Scope of Work ▲</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Task-based content creation</t>
+          <t>Half a domain's surface — ≈ 100 CWT across the six-month internship, produced through the team's agents.</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Domain ownership (set of courses)</t>
+          <t>A domain — its set of courses — across all products; ≈ 200 CWT refreshed per 6-month cycle.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Multiple domains, product coverage</t>
+          <t>Across domains, all products — ≈ 400 CWT per cycle, double an AI Engineer.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Multi-curriculum, product strategy</t>
+          <t>The team's whole surface — every domain's coverage answered for through people.</t>
         </is>
       </c>
     </row>
@@ -2958,7 +3022,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="91" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Foundation</t>
@@ -2976,7 +3040,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Calibration, not a metric — read through the Portfolio Metrics matrix + domain complexity multipliers below.</t>
+          <t>Calibration, not a metric — the scope ladder in one line: Associate = half a domain's surface (≈ 100 CWT across the internship) · AI Engineer = a domain, its set of courses, across all products (≈ 200 CWT / cycle) · Senior = across domains, all products (≈ 400 CWT) · Lead = the team's whole surface. Read through the Portfolio Metrics matrix + domain complexity multipliers below.</t>
         </is>
       </c>
     </row>

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ladder" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates &amp; Scope" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent Scope" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stay Bars" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Areas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Wiring" sheetId="5" state="visible" r:id="rId5"/>
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -790,7 +790,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Progression machinery — the production principle, the A1–A4 Agent Scope scale, promotion gates, and stay bars. Becomes the standing Progression Policy document when formalized.</t>
+          <t>Progression machinery — the production principle, the A1–A4 Agent Scope scale, and the stay-bar rule. Promotion gates live in the Progression Policy &amp; Merit Framework — its own document.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -882,107 +882,34 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Promotion gate</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Requirements (all of them)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="119" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Conversion gate — Associate AI Engineer → AI Engineer, at 6 months</t>
+          <t>Holding the role (the stay bar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>One rule</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>1. Runs assigned agent pipelines end-to-end without supervision — prompts tuned, outputs reviewed, escalations handled (A1–A2 shown).
-2. Judgment demonstrated: the responsible reviewer — their mentoring AI Engineer or Senior — confirms the intern's reviews catch what their own review would catch, sampled on real work through the ramp; they can tell good output from plausible output.
-3. Domain floor: has produced representative content items manually during the ramp — ⚑ propose: ≈ 25% of an AI Engineer's monthly share, held as ramp evidence — you can't review what you can't do.
-4. Decided by: supervising Senior / AI Engineer Lead proposes with ramp evidence; HOD confirms. Package set by HR at conversion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="145" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>AI Engineer → Senior AI Engineer — the 2× bar</t>
+          <t>How you climb lives in the Progression Policy &amp; Merit Framework — its own document; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Per-rung matrices</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>1. Surface ≈ 2× an AI Engineer's — courses × complexity, any mix of depth, breadth, or leverage (A4 agent systems are the leverage route).
-2. Quality held: all their Section B rows at budget, 2+ consecutive cycles.
-3. Leverage visible: Agentic Production Coverage contribution plus falling cost rows for their courses.
-4. People growing: mentorship evidence (Power Performers Created) — guiding work, not owning ratings.
-5. AI Engineer Lead proposes with row evidence; HOD + calibration confirm. Minimum 1 year in role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="145" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer → AI Engineer Lead — people outcomes define the title</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>1. A Lead seat exists — the span rule creates them: ~5–8 members per Lead (number with HR).
-2. Already answering beyond their slice: full-Section-B literacy shown at reviews, Section A lane awareness.
-3. People outcomes proven as a mentor: retention and growth of the people they guided.
-4. Accepts the accountability that defines the title: ratings, retention, growth and hiring for members.
-5. HOD + PM-head calibration confirm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="93" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>AI Engineer Lead → AI Engineer 3 — the org seat</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>1. Org-level surface already held: org-tracker rows shaped, cross-domain standards authored and adopted.
-2. Their team runs without them day to day — the bus-factor test, passed.
-3. By org need, not tenure. HOD proposes; founders / PM-head calibration confirm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Holding the role (the stay bar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>One rule</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>The gates say how you climb; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Per-rung matrices</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>See the Stay Bars tab — each rung's eight rows in the merit-matrix format (Category · Row · Bar · Gate · Weight), with the domain-scaled numbers spelled out.</t>
         </is>
@@ -1016,7 +943,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Holding the role — each rung's stay bar as its eight scored rows (4 output + 4 governance × 12.5%). The gates say how you climb; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
+          <t>Holding the role — each rung's stay bar as its eight scored rows (4 output + 4 governance × 12.5%). How you climb lives in the Progression Policy &amp; Merit Framework — its own document; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1143,7 +1070,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Their topic surface</t>
+          <t>Topic surface</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1197,7 +1124,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Content issues — their items</t>
+          <t>Content issues</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1224,7 +1151,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Recurrence — their items</t>
+          <t>Recurrence</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1278,7 +1205,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Unit costs — their pipelines</t>
+          <t>Unit costs</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2253,7 +2180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>21 progression areas × 4 levels — carried verbatim from the framework except the rows marked ▲ (rewritten agent-first). AI Engineer 3 sits above Lead (org-wide scope); the matrix deliberately stops at Lead.</t>
+          <t>21 progression areas × 4 levels (▲ = rewritten agent-first, Aug 2026). AI Engineer 3 sits above Lead (org-wide scope); the matrix deliberately stops at Lead.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4160,7 +4087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4173,7 +4100,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Calibration: portfolio by level · domain complexity · product baselines · domain catalogue · vocabulary bridge (2026 doc → KPI system)</t>
+          <t>Calibration: portfolio by level · domain complexity · product baselines · domain catalogue</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4833,103 +4760,10 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>2026 doc term</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>In the KPI system</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Functions</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>§10 embedded functions + the content domain teams. “Packaging Teams” = Content Systems &amp; Infra teams (Pavan, Aug 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Stakeholders</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>§7 counterparties — reached through team-view Section C asks, never staffed into lanes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Unchanged — Founders, HODs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Peer Content Teams</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>The other §10 sub-departments (domain teams).</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Support Teams</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Unchanged — HR, Finance, L&amp;D, Facilities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>“Owns” / P&amp;L language</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Translated to the axis rule: Lane (col L) = accountability · Functions (col K) = who works. A Lead answers for the team's Section B; lane numbers stay with lane leads.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B42:E42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -595,7 +595,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI Engineer Ladder — content-department domain teams · August 2026 · five levels: a 6-month internship rung, three employee rungs to Lead, then the org seat. Comp for the changed rungs sits with HR.</t>
+          <t>AI Engineer Ladder — content-department domain teams · August 2026 · five levels: a 6-month internship rung, three employee rungs to Lead, then the product seat (Product Lead — Academy, Intensive or NIAT). All comp bands sit with HR; this version carries no numbers.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -665,12 +665,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>9–24L, band under HR review (the full IC span) | ≥1 year in role before Senior eligibility</t>
+          <t>Band with HR — the full IC span | ≥1 year in role before Senior eligibility</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Manages agents. Owns modules end-to-end and builds new content agents — 2–3 built and adopted by year-end, impact visible in the metrics (A3). One band, covering the full individual-contributor span before Senior.</t>
+          <t>Manages agents. Owns modules end-to-end and builds new content agents — shipped and adopted by year-end, impact visible in the metrics (A3). One band, covering the full individual-contributor span before Senior.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Answers for the Section B velocity + quality rows of the modules they own (their content hours, pieces, issue-recurrence share) — a topic surface of ≈ 100 topics at FullStack / GenAI complexity, refreshed every 6 months, with 2–3 content agents built and adopted (A3).</t>
+          <t>Answers for the Section B velocity + quality rows of the modules they own (their content hours, pieces, issue-recurrence share) — a topic surface of ≈ 100 topics at FullStack / GenAI complexity, refreshed every 6 months, with new content agents built and adopted (A3).</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Band under HR review — new rung | reached through the 2× gate below</t>
+          <t>Band with HR — new rung | reached through the 2× gate</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>24L to 30L | 5+ years</t>
+          <t>Band with HR | reached from Senior AI Engineer — the people route</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -738,30 +738,30 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="126" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer 3 – [Domain Portfolio] Learning Systems</t>
+          <t>Product Lead – [Academy | Intensive | NIAT] Learning Systems</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>30L+ | 7+ years</t>
+          <t>Band with HR | reached from AI Engineer Lead</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Example: "AI Engineer 3 – Portfolio (All Domains) Learning Systems". Sets org-wide content and curriculum strategy. Owns EdTech infrastructure evolution, GenAI content pipelines, and cross-product technical roadmap.</t>
+          <t>Owns one whole product end to end — Academy, Intensive or NIAT. Every domain team shipping into that product rolls up here: its content surface, its learning outcomes, its cost envelope, its roadmap — answered for through the product's Leads. Product-Owner responsibility comes with the seat: the roadmap is set with founders and stakeholders, not just executed. Cross-domain complexity is the growth — end-to-end ownership across every domain the product touches. The deep-IC path above Lead is closed.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Example: "AI Engineer 3 – Portfolio (All Domains) Learning Systems". Sets org-wide content and curriculum strategy. Owns EdTech infrastructure evolution, GenAI content pipelines, and cross-product technical roadmap.</t>
+          <t>Replaces the framework's SDE 3 seat (Aug 2026): the deep-IC path above Lead is closed — growth beyond Lead is product ownership. Where a product carries several Leads, a Senior AI Engineer Lead rung can sit between Lead and this seat — activated by scale, not tenure.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Shapes org-tracker rows and cross-domain standards; portfolio spans teams — reads through §5 department KPIs and org KRAs, not one team view.</t>
+          <t>Answers for one whole product's content surface — every domain team shipping into it — through the product's Leads; reads through §5 department KPIs and the org KRAs, not one team view.</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Design and ship a new content agent end-to-end whose impact holds in the metrics. AI Engineer bar: at least 2–3 built and adopted.</t>
+          <t>Design and ship a new content agent end-to-end whose impact holds in the metrics. AI Engineer bar: new agents built and adopted every year ⚑.</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Intern converts having shown A1 + A2 · AI Engineer reaches A3 within the year · Senior operates at A4 (the leverage route) · Lead runs the team's agent fleet through people · AI Engineer 3 sets the org's agent architecture.</t>
+          <t>Intern converts having shown A1 + A2 · AI Engineer reaches A3 within the year · Senior operates at A4 (the leverage route) · Lead runs the team's agent fleet through people · the Product Lead answers for agent-first across every team shipping into their product.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>How you climb lives in the Progression Policy &amp; Merit Framework — its own document; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
+          <t>How you climb lives in the Progression Policy &amp; Merit Framework — its own document; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at their Baseline Targets, no governance breach. Below target more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>See the Stay Bars tab — each rung's eight rows in the merit-matrix format (Category · Row · Bar · Gate · Weight), with the domain-scaled numbers spelled out.</t>
+          <t>See the Stay Bars tab — each rung's eight rows in the merit-matrix format (Category · Row · Baseline Target · Eligibility Gate · Weight). Numeric values are deliberately blank in this version — they land after the Leads' input round.</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Holding the role — each rung's stay bar as its eight scored rows (4 output + 4 governance × 12.5%). How you climb lives in the Progression Policy &amp; Merit Framework — its own document; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at budget — 100%, no governance breach. Below budget more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
+          <t>Holding the role — each rung's stay bar as its eight scored rows (4 output + 4 governance × 12.5%). How you climb lives in the Progression Policy &amp; Merit Framework — its own document; this says what keeping the seat means. One rule under every bar: your rung's eight scored rows at their Baseline Targets, no governance breach. Below target more than twice in 12 months breaks the bar; two consecutive cycles below starts a structured gap conversation with your Lead — what's missing, the plan, the timeline. A conversation, not a demotion. The tables below are those eight rows, per rung — the same grid the merit rating scores: four output rows, four governance rows, 12.5% each.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>How to read the gate column: Mandatory = the rung's defining requirement · Breach blocks = a breach zeroes that 12.5% slice and blocks eligibility for the cycle · ⚑ = a number not locked yet (a proposed default, adjustable). One gate above every table: a Culture &amp; Values flag in the cycle blocks eligibility whatever the score — culture is rated in the pillars (10%), never scored as a row.  Domain chips — build complexity sets the topic count behind the same ≈ 200 CWT per cycle: Low 1.0× — English · Aptitude · Mathematics Medium 1.5× — Programming · CS Core · DevOps High 2.0× — FullStack · GenAI Very High 2.5× — System Design · DS &amp; Algo · DS / ML.</t>
+          <t>How to read the Eligibility Gate column: Mandatory = the rung's defining requirement · Breach blocks = a breach zeroes that 12.5% slice and blocks eligibility for the cycle · ⚑ = the numeric value is deliberately not printed in this version — Baseline Target values land after the Leads' input round, then founder review; the working defaults are held in the Progression Policy &amp; Merit Framework draft. One gate above every table: a Culture &amp; Values flag in the cycle blocks eligibility whatever the score — culture is rated in the pillars (10%), never scored as a row.  Domain chips — build complexity sets the topic count behind the same ≈ 200 CWT per cycle: Low 1.0× — English · Aptitude · Mathematics Medium 1.5× — Programming · CS Core · DevOps High 2.0× — FullStack · GenAI Very High 2.5× — System Design · DS &amp; Algo · DS / ML.</t>
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
@@ -994,12 +994,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Bar — hold at 100%</t>
+          <t>Baseline Target</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Eligibility Gate</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="43" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Work ships simplified, aesthetic, technically accurate, to the team's standards — accepted first-pass through review</t>
+          <t>Work ships simplified, aesthetic, technically accurate, to the team's standards — no major findings at final QC</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>⚑ ≥ 4 documented before/afters on accuracy, retrieval quality or unit cost — spread across the agents they run, not four tweaks to one</t>
+          <t>Documented before/afters on accuracy, retrieval quality or unit cost — spread across the agents they run, not repeat tweaks to one</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Mandatory ⚑</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>⚑ Half an AI Engineer's — ≈ 100 CWT across the six months, produced through the agents</t>
+          <t>Half an AI Engineer's surface across the six months, produced through the agents</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Mandatory ⚑</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>80% fixed inside the 2-day TAT</t>
+          <t>Fixed inside the turnaround bar</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>≤ 2% — fixes stay fixed</t>
+          <t>Fixes stay fixed — recurrence at the bar</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · coding question on the domain scale ~₹200 FullStack / GenAI up to ₹300 DS &amp; Algo</t>
+          <t>Objective practice item (FIB, MCQ, MMCQ — any type) and coding question each inside its cost bar — scaled by domain complexity FullStack / GenAI DS &amp; Algo</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead (≥ 85% of rows in band) and run day to day by the PM.</t>
+          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead's scoreboard row and run day to day by the PM.</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Bar — hold at 100%</t>
+          <t>Baseline Target</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Eligibility Gate</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>100% of their domain's surface — ≈ 200 CWT each 6-month cycle; the domain = its set of courses, across all products — 200 topics 133 topics 100 topics 80 topics</t>
+          <t>The domain's whole surface refreshed each cycle — the domain = its set of courses, across all products; the topic count behind it scales with the complexity multiplier</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Below 90% blocks ⚑</t>
+          <t>Below floor blocks ⚑</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>90% — with 2–3 content agents built and adopted (A3) by year-end</t>
+          <t>Agent-first is how the domain ships — content agents built and adopted (A3) by year-end</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Agents mandatory</t>
+          <t>Agents mandatory ⚑</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Their domain's students land the org SPI bands — 30% at ≥ 8.0 · 40% at 7.0–8.0 · 30% at 6.0–7.0 (two-sided with Assessments, same as the conversion chain)</t>
+          <t>Their domain's students land the org SPI bands (two-sided with Assessments, same instrument as the conversion chain)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>The domain's learner-facing capabilities built and adopted — evaluation environments included — with Learning Environment Satisfaction holding 4.5 / 5 on them</t>
+          <t>The domain's learner-facing capabilities built and adopted — evaluation environments included — with Learning Environment Satisfaction holding at its bar</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>80% inside the 2-day TAT</t>
+          <t>Issues fixed inside the turnaround bar</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>≤ 2%</t>
+          <t>Fixes stay fixed — recurrence at the bar</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>CpLH ≤ ₹10,000 · objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · coding question under ₹100 baseline ~₹200 FullStack / GenAI up to ₹300 DS &amp; Algo</t>
+          <t>Cost per Learning Hour, objective practice item and coding question each inside its bar — scaled by domain complexity FullStack / GenAI DS &amp; Algo</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Sprint 100% · stakeholder 90%</t>
+          <t>Sprint commitments delivered in full · stakeholder requests fulfilled at the bar</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead (≥ 85% of rows in band) and run day to day by the PM.</t>
+          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead's scoreboard row and run day to day by the PM.</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Bar — hold at 100%</t>
+          <t>Baseline Target</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Eligibility Gate</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Double an AI Engineer — ≈ 400 CWT per cycle, across domains, all products; Senior isn't a medal, it's a load, and the slice doesn't quietly shrink</t>
+          <t>Double an AI Engineer's complexity-weighted surface — across domains, all products; Senior isn't a medal, it's a load, and the slice doesn't quietly shrink</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Below 90% blocks ⚑</t>
+          <t>Below floor blocks ⚑</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>The agents they build or pick run in every domain's production — 90% coverage attributable to them</t>
+          <t>The agents they build or pick run in every domain's production — coverage attributable to them</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>⚑ 6–10 learner-facing initiatives a year, proposed and implemented — Adaptive Objective Practice, Adaptive Coding Practice, Programming Coach and the like — moving the conversion chain for all products</t>
+          <t>A steady flow of learner-facing initiatives proposed and implemented — Adaptive Objective Practice, Adaptive Coding Practice, Programming Coach and the like — moving the conversion chain for all products</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Mandatory ⚑</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>80% inside the 2-day TAT · recurrence ≤ 2%, across the courses they answer for</t>
+          <t>Inside the turnaround bar and fixes stay fixed — across the courses they answer for</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="43" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Every unit cost at or below budget (CpLH ₹10,000 · item ₹3 · coding ₹100–₹300) and falling year on year — ⚑ −40% the target, −10% the minimum direction</t>
+          <t>Every unit cost at or below its bar and falling year on year</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="43" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Sprint 100% · stakeholder 90% — they raise the Section C asks</t>
+          <t>Sprint commitments delivered in full · stakeholder requests fulfilled at the bar — they raise the Section C asks</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>≥ 1 power performer contributed, trailing 12 months (adjustable)</t>
+          <t>Power performers contributed on record, trailing 12 months</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -1800,20 +1800,24 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead (≥ 85% of rows in band) and run day to day by the PM.</t>
+          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead's scoreboard row and run day to day by the PM.</t>
         </is>
       </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="9" t="n"/>
     </row>
-    <row r="42" ht="16" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
           <t>AI Engineer Lead</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr"/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Answers for the whole surface through people — every row here is the team's number, not personal output.</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="9" t="n"/>
@@ -1831,12 +1835,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Bar — hold at 100%</t>
+          <t>Baseline Target</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Eligibility Gate</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1853,152 +1857,152 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
+          <t>Team Tech Stack Freshness</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>The whole surface is covered — every domain in the team's portfolio fresh on its cycle, no domain orphaned</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Below floor blocks ⚑</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>Team Section B in-band rate</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>⚑ propose: ≥ 85% of the team's owned rows at budget (FS pilot: 29 rows)</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>The team scoreboard holds — the agreed share of the team's owned rows at Baseline Target (FS pilot: 29 rows)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory ⚑</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="43" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Business impact — the team's domains</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>The business feels it — the team's Summative and Formative achievement and SPI contribution, the same numbers the org reads (KRA 1)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>At budget ⚑</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="43" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Team Agentic Production Coverage</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>The agent fleet is the team's, not the Lead's — agent-first shipping achieved through people, the fleet maturing up the A-scale</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>A — Output</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Team Tech Stack Freshness</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>100% across the team's whole surface</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Below 90% blocks ⚑</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>People engine — Retention · Power Performers · Hires</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>The people engine runs — people stay, Power Performers come up every cycle, open seats fill fast</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks ⚑</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>A — Output</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Team Agentic Production Coverage</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>90% — run through people, not personally</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>A — Output</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Business impact — the team's domains</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Summative 35% · Formative 23% · SPI band contribution</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>At budget</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="49" ht="56" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Team Retention Rate</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>≥ 90%, trailing 12 months (adjustable)</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Power Performers Created</t>
+          <t>Cost of Operations + unit costs</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>≥ 1 per appraisal cycle (adjustable)</t>
+          <t>The whole operation is affordable — cost of operations at plan, every unit cost at its bar and trending down year on year — run by the team's PM, answered for by the Lead</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -2015,17 +2019,17 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Cost of Operations + Roadmap</t>
+          <t>Team issue flow — resolution + recurrence</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>At plan ⚑ · ≥ 90% ⚑ — run by the team's PM, answered for by the Lead</t>
+          <t>Issues drain team-wide — fixed inside the turnaround bar and they stay fixed, read across the whole surface</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -2034,7 +2038,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="26" customHeight="1">
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -2042,17 +2046,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Stakeholder Fulfillment + Sprint Delivery</t>
+          <t>Roadmap + process + worklogs</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Stakeholder 90% · sprint 100%</t>
+          <t>The machine is documented — roadmap on track, process adherence end-to-end, worklogs current across the team</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks</t>
+          <t>Breach blocks ⚑</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead (≥ 85% of rows in band) and run day to day by the PM.</t>
+          <t>These eight are the decisive slice for this seat — the rest of the team view is answered at team level by the Lead's scoreboard row and run day to day by the PM.</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
@@ -2079,12 +2083,12 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>AI Engineer 3</t>
+          <t>Product Lead (Academy · Intensive · NIAT)</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Reads through department KPIs and org KRAs, not one team view — the bar stays directional until those budgets land: the standards they authored still adopted and alive · portfolio Section B healthy across teams · a Lead bench ready behind them · places the org's learning-systems bets.</t>
+          <t>The deep-IC 'AI Engineer 3' path is closed — beyond Lead, growth is owning a whole product: Academy, Intensive or NIAT, end to end, through its Leads. Product-Owner-type responsibility comes with the seat: the product's roadmap is set with founders and stakeholders, not just executed; cross-domain complexity is the growth. The bar stays directional until the seat is staffed: the product's whole surface fresh through its Leads · the product's team scoreboards healthy · its learning outcomes and cost envelope answered for with founders · a Lead bench ready behind them. Where a product carries several Leads, a Senior AI Engineer Lead rung can sit between Lead and this seat — activated by scale, not tenure.</t>
         </is>
       </c>
       <c r="C54" s="8" t="n"/>
@@ -2099,7 +2103,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Low-refresh domains (English, Aptitude, Mathematics, Programming, CS Core, DS &amp; Algo, DevOps, System Design) run the same eight rows — no slot swaps: Pedagogy Initiative Impact and Learning Systems Design impact are standard occupants for everyone now. The freshness bar is 100% of whatever the audit calls, so a low-churn domain simply has a smaller refresh surface; the freed capacity goes to the LSD and PII rows.</t>
+          <t>Low-refresh domains (English, Aptitude, Mathematics, Programming, CS Core, DS &amp; Algo, DevOps, System Design) run the same eight rows — no slot swaps: Pedagogy Initiative Impact and Learning Systems Design impact are standard occupants for everyone now. The freshness bar is the whole of whatever the audit calls, so a low-churn domain simply has a smaller refresh surface; the freed capacity goes to the LSD and PII rows.</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
@@ -2114,7 +2118,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Cost bars scale with domain complexity, and every number here is adjustable as real costs land: an objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · a coding question under ₹100 baseline — ~₹200 where a question is effectively a project (FullStack, GenAI), up to ₹300 where it ships editorials, brute-force and efficient solutions (DS &amp; Algo).</t>
+          <t>Cost bars scale with domain complexity — an objective practice item (FIB, MCQ, MMCQ — any type) is the cheapest unit; a coding question carries more where a question is effectively a project (FullStack, GenAI) and the most where it ships editorials, brute-force and efficient solutions (DS &amp; Algo). Every bar lands with real cost data.</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
@@ -2180,7 +2184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>21 progression areas × 4 levels (▲ = rewritten agent-first, Aug 2026). AI Engineer 3 sits above Lead (org-wide scope); the matrix deliberately stops at Lead.</t>
+          <t>21 progression areas × 4 levels (▲ = rewritten agent-first, Aug 2026). The Product Lead seat (Academy · Intensive · NIAT) sits above Lead; the matrix deliberately stops at Lead.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2463,7 +2467,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Builds new content agents end-to-end — at least 2–3 built and adopted, impact visible in the metrics (A3).</t>
+          <t>Builds new content agents end-to-end — shipped and adopted, impact visible in the metrics (A3).</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">

--- a/docs/handoff/artifacts/role_cards.xlsx
+++ b/docs/handoff/artifacts/role_cards.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>See the Stay Bars tab — each rung's eight rows in the merit-matrix format (Category · Row · Baseline Target · Eligibility Gate · Weight). Numeric values are deliberately blank in this version — they land after the Leads' input round.</t>
+          <t>See the Stay Bars tab — each rung's eight rows in the merit-matrix format, with the Baseline Target printed both ways (tentative number · what the row means). The numbers are the working values for the Leads' input round — nothing locked until it closes, then founder review.</t>
         </is>
       </c>
     </row>
@@ -930,14 +930,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,6 +951,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -959,12 +961,13 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>How to read the Eligibility Gate column: Mandatory = the rung's defining requirement · Breach blocks = a breach zeroes that 12.5% slice and blocks eligibility for the cycle · ⚑ = the numeric value is deliberately not printed in this version — Baseline Target values land after the Leads' input round, then founder review; the working defaults are held in the Progression Policy &amp; Merit Framework draft. One gate above every table: a Culture &amp; Values flag in the cycle blocks eligibility whatever the score — culture is rated in the pillars (10%), never scored as a row.  Domain chips — build complexity sets the topic count behind the same ≈ 200 CWT per cycle: Low 1.0× — English · Aptitude · Mathematics Medium 1.5× — Programming · CS Core · DevOps High 2.0× — FullStack · GenAI Very High 2.5× — System Design · DS &amp; Algo · DS / ML.</t>
+          <t>Baseline Targets carry two readings: the tentative number — the working value for the Leads' input round; nothing is locked, every number can move before founder review, and ⚑ marks a proposed default that hasn't been ruled yet — and the plain-words meaning of the same row. How to read the Eligibility Gate column: Mandatory = the rung's defining requirement · Breach blocks = a breach zeroes that 12.5% slice and blocks eligibility for the cycle. Rows sit in the same order on every rung — output: the surface · the agents · learning impact · learning systems; governance: issues · costs · delivery · people, where the rung carries a people row. One gate above every table: a Culture &amp; Values flag in the cycle blocks eligibility whatever the score — culture is rated in the pillars (10%), never scored as a row.  Domain chips — build complexity sets the topic count behind the same ≈ 200 CWT per cycle: Low 1.0× — English · Aptitude · Mathematics Medium 1.5× — Programming · CS Core · DevOps High 2.0× — FullStack · GenAI Very High 2.5× — System Design · DS &amp; Algo · DS / ML.</t>
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
-      <c r="E2" s="9" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="9" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
@@ -979,7 +982,8 @@
       </c>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -994,21 +998,26 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Baseline Target</t>
+          <t>Baseline Target — tentative number</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>What the row means</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Eligibility Gate</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="43" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1016,20 +1025,25 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Content quality &amp; standards</t>
+          <t>Topic surface</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Work ships simplified, aesthetic, technically accurate, to the team's standards — no major findings at final QC</t>
+          <t>⚑ ≈ 100 CWT across the six months — half an AI Engineer's surface, produced through the agents</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>Half an AI Engineer's surface across the six months, produced through the agents</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1048,21 +1062,26 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>⚑ ≥ 4 documented before/afters on accuracy, retrieval quality or unit cost — spread across the agents they run, not repeat tweaks to one</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
           <t>Documented before/afters on accuracy, retrieval quality or unit cost — spread across the agents they run, not repeat tweaks to one</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Mandatory ⚑</t>
-        </is>
-      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="43" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1070,26 +1089,31 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Topic surface</t>
+          <t>Content quality &amp; standards</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Half an AI Engineer's surface across the six months, produced through the agents</t>
+          <t>— (no numeric form)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Mandatory ⚑</t>
+          <t>Work ships simplified, aesthetic, technically accurate, to the team's standards — no major findings at final QC</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="69" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1102,15 +1126,20 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t>— (no numeric form)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
           <t>Runs the feedback agents — reactive and proactive channels, every dimension — and outputs the plan; review inputs logged by the mentoring AI Engineer reach zero by the final two months</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1129,15 +1158,20 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t>80% fixed inside the 2-day TAT</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
           <t>Fixed inside the turnaround bar</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1156,21 +1190,26 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>≤ 2% — fixes stay fixed</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
           <t>Fixes stay fixed — recurrence at the bar</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="56" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1178,47 +1217,57 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>Unit costs</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Objective practice item (FIB, MCQ, MMCQ — any type) ≤ ₹3 · coding question inside its domain bar ~₹200 FullStack / GenAI up to ₹300 DS &amp; Algo</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Objective practice item (FIB, MCQ, MMCQ — any type) and coding question each inside its cost bar — scaled by domain complexity FullStack / GenAI DS &amp; Algo</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>Process adherence</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>— (no numeric form)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>The team's guidelines followed end-to-end — checklists, review sheets, worklogs current</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Breach blocks</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="43" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Unit costs</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Objective practice item (FIB, MCQ, MMCQ — any type) and coding question each inside its cost bar — scaled by domain complexity FullStack / GenAI DS &amp; Algo</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1237,7 +1286,8 @@
       </c>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="9" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1252,7 +1302,8 @@
       </c>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
-      <c r="E15" s="9" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="9" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -1263,7 +1314,8 @@
       <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1278,21 +1330,26 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Baseline Target</t>
+          <t>Baseline Target — tentative number</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
+          <t>What the row means</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
           <t>Eligibility Gate</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="43" customHeight="1">
+    <row r="19" ht="56" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1305,15 +1362,20 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
+          <t>100% of the domain's surface each 6-month cycle — ⚑ ≈ 200 CWT: 200 topics 133 100 80</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
           <t>The domain's whole surface refreshed each cycle — the domain = its set of courses, across all products; the topic count behind it scales with the complexity multiplier</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Below floor blocks ⚑</t>
-        </is>
-      </c>
       <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Below 90% blocks ⚑</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1332,21 +1394,26 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
+          <t>90% agent-first · 2–3 content agents built and adopted (A3) by year-end</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
           <t>Agent-first is how the domain ships — content agents built and adopted (A3) by year-end</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Agents mandatory ⚑</t>
-        </is>
-      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>Agents mandatory</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="43" customHeight="1">
+    <row r="21" ht="56" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1359,21 +1426,26 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
+          <t>Students land the org SPI bands — 30% ≥ 8.0 · 40% 7.0–8.0 · 30% 6.0–7.0 (two-sided with Assessments, same instrument as the conversion chain)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
           <t>Their domain's students land the org SPI bands (two-sided with Assessments, same instrument as the conversion chain)</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>At the bands ⚑</t>
-        </is>
-      </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>At the bands</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="43" customHeight="1">
+    <row r="22" ht="56" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1386,15 +1458,20 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
+          <t>The domain's learner-facing capabilities built and adopted — Learning Environment Satisfaction holding ⚑ 4.5 / 5</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
           <t>The domain's learner-facing capabilities built and adopted — evaluation environments included — with Learning Environment Satisfaction holding at its bar</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>At budget ⚑</t>
-        </is>
-      </c>
       <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>At budget</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1413,15 +1490,20 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
+          <t>80% fixed inside the 2-day TAT</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
           <t>Issues fixed inside the turnaround bar</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1440,21 +1522,26 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
+          <t>≤ 2% — fixes stay fixed</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
           <t>Fixes stay fixed — recurrence at the bar</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="43" customHeight="1">
+    <row r="25" ht="56" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1467,15 +1554,20 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
+          <t>Cost per Learning Hour ≤ ₹10,000 · objective practice item ≤ ₹3 · coding question from a ₹100 base ~₹200 FullStack / GenAI up to ₹300 DS &amp; Algo</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
           <t>Cost per Learning Hour, objective practice item and coding question each inside its bar — scaled by domain complexity FullStack / GenAI DS &amp; Algo</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1494,15 +1586,20 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
+          <t>Sprint 100% · stakeholder fulfillment 90%</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
           <t>Sprint commitments delivered in full · stakeholder requests fulfilled at the bar</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1521,7 +1618,8 @@
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
-      <c r="E27" s="9" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="9" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -1536,7 +1634,8 @@
       </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
-      <c r="E28" s="9" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="9" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
@@ -1547,7 +1646,8 @@
       <c r="B30" s="7" t="inlineStr"/>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="n"/>
-      <c r="E30" s="9" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1562,21 +1662,26 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Baseline Target</t>
+          <t>Baseline Target — tentative number</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
+          <t>What the row means</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>Eligibility Gate</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="43" customHeight="1">
+    <row r="32" ht="56" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1589,21 +1694,26 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
+          <t>≈ 400 CWT per cycle — double an AI Engineer, across domains, all products; the slice doesn't quietly shrink</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
           <t>Double an AI Engineer's complexity-weighted surface — across domains, all products; Senior isn't a medal, it's a load, and the slice doesn't quietly shrink</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Below floor blocks ⚑</t>
-        </is>
-      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>Below 90% blocks ⚑</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="134" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1616,21 +1726,26 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>The agents they build or pick run in every domain's production — coverage attributable to them</t>
+          <t>At least 2–3 agents of this class built and adopted 100% by all teams — e.g. a Slides Creation Workflow · QC agents like a Practice Question Production Evaluator or a Pedagogy Guidelines Evaluator · a Configurator agent that pushes finished content onto the learning portal over MCP — a considerable, attributable lift in Agentic Production Coverage across teams; improving one, or adapting it to a new domain's use-case, counts</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>The agents they build or pick run in every domain's production — the kind of agent: a Slides Creation Workflow · QC agents like a Practice Question Production Evaluator or a Pedagogy Guidelines Evaluator · a Configurator agent that pushes finished content onto the learning portal over MCP. Improving one, or adapting it to a new domain's use-case, counts the same as building new</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="69" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1638,47 +1753,57 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
+          <t>Pedagogy Initiative Impact</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Every initiative carries an agreed baseline before launch · the SPI bands hold — 30% ≥ 8.0 · 40% 7.0–8.0 · 30% 6.0–7.0 — across every domain they touch</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Every LSD initiative pedagogically grounded — baseline agreed before launch — and the SPI bands hold across every domain they touch; the surface, not the activity, separates this from an AI Engineer</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>At the bands</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="69" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>A — Output</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>Learning Systems Design impact</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>8–10 learner-facing initiatives a year, proposed and implemented — Adaptive Objective Practice, Adaptive Coding Practice, Programming Coach and the like — moving the conversion chain for all products</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>A steady flow of learner-facing initiatives proposed and implemented — Adaptive Objective Practice, Adaptive Coding Practice, Programming Coach and the like — moving the conversion chain for all products</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Mandatory ⚑</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>A — Output</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Pedagogy Initiative Impact</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Those initiatives pedagogically grounded — baseline agreed before launch — and the SPI bands hold across every domain they touch; the surface, not the activity, separates this from an AI Engineer</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>At the bands ⚑</t>
-        </is>
-      </c>
       <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1697,21 +1822,26 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
+          <t>80% inside the 2-day TAT · recurrence ≤ 2% — across the courses they answer for</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
           <t>Inside the turnaround bar and fixes stay fixed — across the courses they answer for</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="56" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1724,15 +1854,20 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
+          <t>Every unit cost at or below its bar (CpLH ₹10,000 · item ₹3 · coding ₹100–₹300) and falling year on year — −40% per year the target, −10% the minimum direction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
           <t>Every unit cost at or below its bar and falling year on year</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1751,21 +1886,26 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
+          <t>Sprint 100% · stakeholder fulfillment 90% — they raise the Section C asks</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
           <t>Sprint commitments delivered in full · stakeholder requests fulfilled at the bar — they raise the Section C asks</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="43" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1773,20 +1913,25 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Mentorship on record</t>
+          <t>Power Performers Created</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Power performers contributed on record, trailing 12 months</t>
+          <t>≥ 1 Power Performer created per appraisal cycle</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Breach blocks ⚑</t>
+          <t>People they mentor become the team's next Power Performers — created on record, through guiding real work</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1805,7 +1950,8 @@
       </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
-      <c r="E40" s="9" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="9" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
@@ -1820,7 +1966,8 @@
       </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
-      <c r="E42" s="9" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1835,21 +1982,26 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Baseline Target</t>
+          <t>Baseline Target — tentative number</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
+          <t>What the row means</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
           <t>Eligibility Gate</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="43" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1862,21 +2014,26 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
+          <t>100% of whatever the audit calls, across every domain in the team's portfolio — no domain orphaned</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
           <t>The whole surface is covered — every domain in the team's portfolio fresh on its cycle, no domain orphaned</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Below floor blocks ⚑</t>
-        </is>
-      </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
+          <t>Below 90% blocks ⚑</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" ht="43" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1884,26 +2041,31 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Team Section B in-band rate</t>
+          <t>Team Agentic Production Coverage</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>The team scoreboard holds — the agreed share of the team's owned rows at Baseline Target (FS pilot: 29 rows)</t>
+          <t>90% blended across the team — the fleet maturing up the A-scale, agent-first through people</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Mandatory ⚑</t>
+          <t>The agent fleet is the team's, not the Lead's — agent-first shipping achieved through people, the fleet maturing up the A-scale</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="43" customHeight="1">
+    <row r="46" ht="56" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
           <t>A — Output</t>
@@ -1916,15 +2078,20 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
+          <t>Summative 35% · Formative 23% · SPI contribution at team level — the same numbers the org reads: KRA 1 bands 30% ≥ 8.0 · 40% 7.0–8.0 · 30% 6.0–7.0; Graded Assessment for NIAT ⚑</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
           <t>The business feels it — the team's Summative and Formative achievement and SPI contribution, the same numbers the org reads (KRA 1)</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>At budget ⚑</t>
-        </is>
-      </c>
       <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>At budget</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -1938,26 +2105,31 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Team Agentic Production Coverage</t>
+          <t>Team Section B in-band rate</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>The agent fleet is the team's, not the Lead's — agent-first shipping achieved through people, the fleet maturing up the A-scale</t>
+          <t>⚑ ≥ 85% of the team's owned rows at Baseline Target (FS pilot: 29 rows)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>The team scoreboard holds — the agreed share of the team's owned rows at Baseline Target (FS pilot: 29 rows)</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="43" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
           <t>B — Governance</t>
@@ -1965,101 +2137,121 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
+          <t>Team issue flow — resolution + recurrence</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>80% inside the 2-day TAT team-wide · recurrence ≤ 2% — read across the whole surface</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Issues drain team-wide — fixed inside the turnaround bar and they stay fixed, read across the whole surface</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="69" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Cost of Operations + unit costs</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Cost of Operations at plan ⚑ · every unit cost at its bar (CpLH ₹10,000 · item ₹3 · coding ₹100–₹300), trending −10% per year minimum toward −40% — run by the team's PM, answered for by the Lead</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>The whole operation is affordable — cost of operations at plan, every unit cost at its bar and trending down year on year — run by the team's PM, answered for by the Lead</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="43" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap + process + worklogs</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Roadmap ⚑ ≥ 90% completion · process adherence end-to-end · worklogs current across the team</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>The machine is documented — roadmap on track, process adherence end-to-end, worklogs current across the team</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="56" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>B — Governance</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>People engine — Retention · Power Performers · Hires</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Retention ≥ 90% trailing 12 months (internal transfers don't count) · ≥ 2 Power Performers per appraisal cycle · open seats fill fast — hire TAT with the PM</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>The people engine runs — people stay, Power Performers come up every cycle, open seats fill fast</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="56" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Cost of Operations + unit costs</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>The whole operation is affordable — cost of operations at plan, every unit cost at its bar and trending down year on year — run by the team's PM, answered for by the Lead</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Team issue flow — resolution + recurrence</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Issues drain team-wide — fixed inside the turnaround bar and they stay fixed, read across the whole surface</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>B — Governance</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap + process + worklogs</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>The machine is documented — roadmap on track, process adherence end-to-end, worklogs current across the team</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Breach blocks ⚑</t>
-        </is>
-      </c>
       <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Breach blocks</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
@@ -2078,7 +2270,8 @@
       </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
-      <c r="E52" s="9" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="9" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
@@ -2093,7 +2286,8 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
-      <c r="E54" s="9" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="9" t="n"/>
     </row>
     <row r="56" ht="56" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
@@ -2108,7 +2302,8 @@
       </c>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
-      <c r="E56" s="9" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="9" t="n"/>
     </row>
     <row r="57" ht="56" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -2123,7 +2318,8 @@
       </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
-      <c r="E57" s="9" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="9" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
@@ -2138,26 +2334,27 @@
       </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
-      <c r="E58" s="9" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B52:F52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
